--- a/articolo_04_micropali/Micropali_BustamanteDoix_v1.0.xlsx
+++ b/articolo_04_micropali/Micropali_BustamanteDoix_v1.0.xlsx
@@ -8,32 +8,34 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Documents\_Francisco\_GitHub\franciscojmendez_Risorse\articolo_04_micropali\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81B6BC09-B00B-4D5B-B3F3-42071BDFAEFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B92F618-7AC8-4E27-B1A9-C739878B7CB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="710" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7320" yWindow="0" windowWidth="21600" windowHeight="13785" tabRatio="710" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DB_Abachi" sheetId="1" state="hidden" r:id="rId1"/>
     <sheet name="Credits" sheetId="14" r:id="rId2"/>
     <sheet name="DATI_INPUT" sheetId="2" r:id="rId3"/>
-    <sheet name="CALCOLO-Qmedio" sheetId="3" r:id="rId4"/>
-    <sheet name="CALCOLO-Qminimo" sheetId="4" r:id="rId5"/>
-    <sheet name="NTC2018" sheetId="5" r:id="rId6"/>
-    <sheet name="Grafico-SG" sheetId="10" r:id="rId7"/>
-    <sheet name="Grafico-AL" sheetId="11" r:id="rId8"/>
-    <sheet name="Grafico-MC" sheetId="12" r:id="rId9"/>
-    <sheet name="Grafico-RA" sheetId="13" r:id="rId10"/>
-    <sheet name="ABACO-SG" sheetId="6" state="hidden" r:id="rId11"/>
-    <sheet name="ABACO-AL" sheetId="7" state="hidden" r:id="rId12"/>
-    <sheet name="ABACO-MC" sheetId="8" state="hidden" r:id="rId13"/>
-    <sheet name="ABACO-RA" sheetId="9" state="hidden" r:id="rId14"/>
+    <sheet name="TAB_ALPHA" sheetId="15" r:id="rId4"/>
+    <sheet name="CALCOLO-Qmedio" sheetId="3" r:id="rId5"/>
+    <sheet name="CALCOLO-Qminimo" sheetId="4" r:id="rId6"/>
+    <sheet name="NTC2018" sheetId="5" r:id="rId7"/>
+    <sheet name="Grafico-SG" sheetId="10" r:id="rId8"/>
+    <sheet name="Grafico-AL" sheetId="11" r:id="rId9"/>
+    <sheet name="Grafico-MC" sheetId="12" r:id="rId10"/>
+    <sheet name="Grafico-RA" sheetId="13" r:id="rId11"/>
+    <sheet name="ABACO-SG" sheetId="6" state="hidden" r:id="rId12"/>
+    <sheet name="ABACO-AL" sheetId="7" state="hidden" r:id="rId13"/>
+    <sheet name="ABACO-MC" sheetId="8" state="hidden" r:id="rId14"/>
+    <sheet name="ABACO-RA" sheetId="9" state="hidden" r:id="rId15"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'CALCOLO-Qmedio'!$A$1:$H$22</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'CALCOLO-Qminimo'!$A$1:$H$22</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'CALCOLO-Qmedio'!$A$1:$H$22</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'CALCOLO-Qminimo'!$A$1:$H$22</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">Credits!$A$1:$B$19</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">DATI_INPUT!$A$1:$M$22</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">'NTC2018'!$A$1:$G$29</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'NTC2018'!$A$1:$G$29</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">TAB_ALPHA!$A$1:$D$20</definedName>
   </definedNames>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -56,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="163">
   <si>
     <t>Abaco</t>
   </si>
@@ -125,9 +127,6 @@
   </si>
   <si>
     <t>B  |  DATI PER STRATO</t>
-  </si>
-  <si>
-    <t>Tipo terreno: SG=Sabbie/Ghiaie, AL=Argille/Limi, MC=Marne/Calcari, RA=Rocce Alterate. α* = valore suggerito da Bustamante (automatico). α usato = modificabile dall'utente. Usa NSPT?=Sì → GetPl_fromNSPT() (non disponibile per RA: inserire pl diretto). Se pl=0 o vuoto → Qs,i=0. Lasciare vuote le righe non utilizzate.</t>
   </si>
   <si>
     <t>Strato</t>
@@ -414,15 +413,9 @@
     <t>Articolo</t>
   </si>
   <si>
-    <t>[LINK]</t>
-  </si>
-  <si>
     <t>Repository</t>
   </si>
   <si>
-    <t>github.com/FraJoMen/franciscojmendez_Risorse</t>
-  </si>
-  <si>
     <t>FONTE SCIENTIFICA</t>
   </si>
   <si>
@@ -454,6 +447,128 @@
   </si>
   <si>
     <t>Sì</t>
+  </si>
+  <si>
+    <t>Tabella 1 – Valori del coefficiente di sbulbatura α e delle quantità minime di malta Vi proposti da Bustamante–Doix (1985)</t>
+  </si>
+  <si>
+    <t>Terreno</t>
+  </si>
+  <si>
+    <t>Coefficiente α</t>
+  </si>
+  <si>
+    <t>Quantità minima di malta consigliata Vi</t>
+  </si>
+  <si>
+    <t>Ghiaia</t>
+  </si>
+  <si>
+    <t>1.8</t>
+  </si>
+  <si>
+    <t>da 1.3 a 1.4</t>
+  </si>
+  <si>
+    <t>1.5 Vs</t>
+  </si>
+  <si>
+    <t>Ghiaia sabbiosa</t>
+  </si>
+  <si>
+    <t>da 1.6 a 1.8</t>
+  </si>
+  <si>
+    <t>Sabbia ghiaiosa</t>
+  </si>
+  <si>
+    <t>da 1.5 a 1.6</t>
+  </si>
+  <si>
+    <t>da 1.2 a 1.3</t>
+  </si>
+  <si>
+    <t>Sabbia grossolana</t>
+  </si>
+  <si>
+    <t>da 1.4 a 1.5</t>
+  </si>
+  <si>
+    <t>da 1.1 a 1.2</t>
+  </si>
+  <si>
+    <t>Sabbia media</t>
+  </si>
+  <si>
+    <t>Sabbia fine</t>
+  </si>
+  <si>
+    <t>Sabbia limosa</t>
+  </si>
+  <si>
+    <t>(1.5 ÷ 2) Vs per IRS
+1.5 Vs per IGU</t>
+  </si>
+  <si>
+    <t>Limo</t>
+  </si>
+  <si>
+    <t>da 1.4 a 1.6</t>
+  </si>
+  <si>
+    <t>2 Vs per IRS
+1.5 Vs per IGU</t>
+  </si>
+  <si>
+    <t>Argilla</t>
+  </si>
+  <si>
+    <t>da 1.8 a 2</t>
+  </si>
+  <si>
+    <t>1.2</t>
+  </si>
+  <si>
+    <t>(2.5 ÷ 3) Vs per IRS
+(1.5 ÷ 2) Vs per IGU</t>
+  </si>
+  <si>
+    <t>Marna</t>
+  </si>
+  <si>
+    <t>(1.5 ÷ 2) Vs per strato compatto
+(2 ÷ 6) Vs o più, se strato fratturato</t>
+  </si>
+  <si>
+    <t>Marno-calcare</t>
+  </si>
+  <si>
+    <t>Creta alterata o frammentata</t>
+  </si>
+  <si>
+    <t>Roccia alterata o frammentata</t>
+  </si>
+  <si>
+    <t>1.1</t>
+  </si>
+  <si>
+    <t>(1.1 ÷ 1.5) Vs se strato finemente fessurato
+2 o più, se strato fratturato</t>
+  </si>
+  <si>
+    <t>Vs = volume teorico del fusto del micropalo  |  IRS = iniezione ripetuta e selettiva  |  IGU = iniezione globale unica</t>
+  </si>
+  <si>
+    <t>Fonte: Bustamante M. &amp; Doix B. (1985) – Une méthode pour le calcul des tirants et des micropieux injectés.</t>
+  </si>
+  <si>
+    <t>Tipo terreno: SG=Sabbie/Ghiaie, AL=Argille/Limi, MC=Marne/Calcari, RA=Rocce Alterate. α* = media stimata per categoria di terreno. α usato = modificabile dall'utente (vedi TAB_ALPHA per dettaglio). Usa NSPT?=Sì → GetPl_fromNSPT() (non disponibile per RA: inserire pl diretto). Se pl=0 o vuoto → Qs,i=0. Lasciare vuote le righe non utilizzate.</t>
+  </si>
+  <si>
+    <t>https://www.franciscojmendez.com/il-metodo-bustamante-doix-per-il-calcolo-dei-micropali/</t>
+  </si>
+  <si>
+    <t>https://github.com/FraJoMen/franciscojmendez_Risorse/tree/main/articolo_04_micropali</t>
   </si>
 </sst>
 </file>
@@ -464,13 +579,20 @@
     <numFmt numFmtId="164" formatCode="0.000"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="28" x14ac:knownFonts="1">
+  <fonts count="34" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -630,13 +752,6 @@
       <family val="2"/>
     </font>
     <font>
-      <u/>
-      <sz val="10"/>
-      <color rgb="FF1F4E79"/>
-      <name val="Arial Narrow"/>
-      <family val="2"/>
-    </font>
-    <font>
       <i/>
       <sz val="9"/>
       <color rgb="FF7F7F7F"/>
@@ -650,8 +765,46 @@
       <name val="Arial Narrow"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF1F4E79"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FF595959"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="15">
+  <fills count="19">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -736,8 +889,28 @@
         <bgColor rgb="FFFFF2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2E75B6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDEEAF1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -788,128 +961,142 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB8CCE4"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB8CCE4"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB8CCE4"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB8CCE4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="9" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="9" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="13" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="9" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="8" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="9" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="8" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="9" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="18" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="19" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="19" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="18" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="19" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="19" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="8" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="9" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="9" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="5" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="10" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="6" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="165" fontId="13" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="24" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -919,88 +1106,122 @@
     <xf numFmtId="0" fontId="26" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="29" fillId="16" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="17" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="17" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="18" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="18" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="13" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="15" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="18" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="3">
+    <cellStyle name="Collegamento ipertestuale" xfId="2" builtinId="8"/>
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
+    <cellStyle name="Normale 2" xfId="1" xr:uid="{63906859-67DE-4A25-BB1A-CC331B1953A9}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -5810,7 +6031,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.48321706743369969</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>#N/A</c:v>
@@ -5919,7 +6140,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.41883573812024932</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>#N/A</c:v>
@@ -6170,7 +6391,8 @@
 <chartsheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" xr:uid="{2EF0404A-4E0F-4985-AA78-8B3D9CAB3EDC}">
   <sheetPr codeName="Grafico1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </chartsheet>
 </file>
 
@@ -6178,7 +6400,8 @@
 <chartsheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" xr:uid="{ECB2F78E-B215-4545-9BCC-767074AB79FD}">
   <sheetPr codeName="Grafico2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </chartsheet>
 </file>
 
@@ -6186,7 +6409,8 @@
 <chartsheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" xr:uid="{73CB1968-6846-4250-8271-45FE9B735EBD}">
   <sheetPr codeName="Grafico3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </chartsheet>
 </file>
 
@@ -6194,7 +6418,8 @@
 <chartsheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" xr:uid="{D1D24D2D-1459-4D83-BCD4-271C669F27EB}">
   <sheetPr codeName="Grafico4"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </chartsheet>
 </file>
 
@@ -6202,7 +6427,7 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:absoluteAnchor>
     <xdr:pos x="0" y="0"/>
-    <xdr:ext cx="9293311" cy="6066824"/>
+    <xdr:ext cx="8376508" cy="5469924"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Grafico 1">
@@ -6235,7 +6460,7 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:absoluteAnchor>
     <xdr:pos x="0" y="0"/>
-    <xdr:ext cx="9293311" cy="6066824"/>
+    <xdr:ext cx="8376508" cy="5469924"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Grafico 1">
@@ -6268,7 +6493,7 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:absoluteAnchor>
     <xdr:pos x="0" y="0"/>
-    <xdr:ext cx="9293311" cy="6066824"/>
+    <xdr:ext cx="8376508" cy="5469924"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Grafico 1">
@@ -6301,7 +6526,7 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:absoluteAnchor>
     <xdr:pos x="0" y="0"/>
-    <xdr:ext cx="9305925" cy="6076950"/>
+    <xdr:ext cx="9297924" cy="6071616"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Grafico 1">
@@ -7272,6 +7497,543 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <sheetPr codeName="Foglio8"/>
+  <dimension ref="A1:N22"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="8" width="9" customWidth="1"/>
+    <col min="9" max="9" width="7" customWidth="1"/>
+    <col min="10" max="10" width="16" customWidth="1"/>
+    <col min="11" max="14" width="11" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="56" t="s">
+        <v>96</v>
+      </c>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="56"/>
+      <c r="J1" s="56"/>
+      <c r="K1" s="56"/>
+      <c r="L1" s="56"/>
+      <c r="M1" s="56"/>
+      <c r="N1" s="56"/>
+    </row>
+    <row r="2" spans="1:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="53" t="s">
+        <v>97</v>
+      </c>
+      <c r="B2" s="53"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="53"/>
+      <c r="L2" s="53"/>
+      <c r="M2" s="53"/>
+      <c r="N2" s="53"/>
+    </row>
+    <row r="4" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="26" t="s">
+        <v>98</v>
+      </c>
+      <c r="C4" s="26" t="s">
+        <v>99</v>
+      </c>
+      <c r="E4" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="G4" s="26" t="s">
+        <v>86</v>
+      </c>
+      <c r="I4" s="27" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="28" t="s">
+        <v>88</v>
+      </c>
+      <c r="B5" s="28" t="s">
+        <v>89</v>
+      </c>
+      <c r="C5" s="28" t="s">
+        <v>88</v>
+      </c>
+      <c r="D5" s="28" t="s">
+        <v>89</v>
+      </c>
+      <c r="E5" s="28" t="s">
+        <v>88</v>
+      </c>
+      <c r="F5" s="28" t="s">
+        <v>89</v>
+      </c>
+      <c r="G5" s="28" t="s">
+        <v>88</v>
+      </c>
+      <c r="H5" s="28" t="s">
+        <v>89</v>
+      </c>
+      <c r="I5" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="J5" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="K5" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="L5" s="29" t="s">
+        <v>90</v>
+      </c>
+      <c r="M5" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="N5" s="29" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>1.0162</v>
+      </c>
+      <c r="B6">
+        <v>0.1928</v>
+      </c>
+      <c r="C6">
+        <v>1.0189999999999999</v>
+      </c>
+      <c r="D6">
+        <v>0.1484</v>
+      </c>
+      <c r="E6">
+        <v>1.204</v>
+      </c>
+      <c r="F6">
+        <v>0.2288</v>
+      </c>
+      <c r="G6">
+        <v>3.5346000000000002</v>
+      </c>
+      <c r="H6">
+        <v>0.44169999999999998</v>
+      </c>
+      <c r="I6" s="30" t="e">
+        <f>IF(DATI_INPUT!D13="MC",DATI_INPUT!A13,NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J6" s="31" t="e">
+        <f>IF(DATI_INPUT!D13="MC",DATI_INPUT!B13,NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K6" s="32" t="e">
+        <f>IF(DATI_INPUT!D13="MC",IFERROR('CALCOLO-Qmedio'!F10,NA()),NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L6" s="32" t="e">
+        <f>IF(DATI_INPUT!D13="MC",IFERROR('CALCOLO-Qmedio'!G10,NA()),NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="M6" s="32" t="e">
+        <f>IF(DATI_INPUT!D13="MC",IFERROR('CALCOLO-Qminimo'!F10,NA()),NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="N6" s="32" t="e">
+        <f>IF(DATI_INPUT!D13="MC",IFERROR('CALCOLO-Qminimo'!G10,NA()),NA())</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>7.9931999999999999</v>
+      </c>
+      <c r="B7">
+        <v>0.68769999999999998</v>
+      </c>
+      <c r="C7">
+        <v>7.9814999999999996</v>
+      </c>
+      <c r="D7">
+        <v>0.50060000000000004</v>
+      </c>
+      <c r="E7">
+        <v>1.5159</v>
+      </c>
+      <c r="F7">
+        <v>0.24399999999999999</v>
+      </c>
+      <c r="G7">
+        <v>5.4132999999999996</v>
+      </c>
+      <c r="H7">
+        <v>0.36430000000000001</v>
+      </c>
+      <c r="I7" s="33" t="e">
+        <f>IF(DATI_INPUT!D14="MC",DATI_INPUT!A14,NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J7" s="34" t="e">
+        <f>IF(DATI_INPUT!D14="MC",DATI_INPUT!B14,NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K7" s="35" t="e">
+        <f>IF(DATI_INPUT!D14="MC",IFERROR('CALCOLO-Qmedio'!F11,NA()),NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L7" s="35" t="e">
+        <f>IF(DATI_INPUT!D14="MC",IFERROR('CALCOLO-Qmedio'!G11,NA()),NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="M7" s="35" t="e">
+        <f>IF(DATI_INPUT!D14="MC",IFERROR('CALCOLO-Qminimo'!F11,NA()),NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="N7" s="35" t="e">
+        <f>IF(DATI_INPUT!D14="MC",IFERROR('CALCOLO-Qminimo'!G11,NA()),NA())</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E8">
+        <v>1.8716999999999999</v>
+      </c>
+      <c r="F8">
+        <v>0.29409999999999997</v>
+      </c>
+      <c r="G8">
+        <v>5.6273999999999997</v>
+      </c>
+      <c r="H8">
+        <v>0.3634</v>
+      </c>
+      <c r="I8" s="30" t="e">
+        <f>IF(DATI_INPUT!D15="MC",DATI_INPUT!A15,NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J8" s="31" t="e">
+        <f>IF(DATI_INPUT!D15="MC",DATI_INPUT!B15,NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K8" s="32" t="e">
+        <f>IF(DATI_INPUT!D15="MC",IFERROR('CALCOLO-Qmedio'!F12,NA()),NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L8" s="32" t="e">
+        <f>IF(DATI_INPUT!D15="MC",IFERROR('CALCOLO-Qmedio'!G12,NA()),NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="M8" s="32" t="e">
+        <f>IF(DATI_INPUT!D15="MC",IFERROR('CALCOLO-Qminimo'!F12,NA()),NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="N8" s="32" t="e">
+        <f>IF(DATI_INPUT!D15="MC",IFERROR('CALCOLO-Qminimo'!G12,NA()),NA())</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E9">
+        <v>1.8864000000000001</v>
+      </c>
+      <c r="F9">
+        <v>0.25209999999999999</v>
+      </c>
+      <c r="I9" s="33" t="e">
+        <f>IF(DATI_INPUT!D16="MC",DATI_INPUT!A16,NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J9" s="34" t="e">
+        <f>IF(DATI_INPUT!D16="MC",DATI_INPUT!B16,NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K9" s="35" t="e">
+        <f>IF(DATI_INPUT!D16="MC",IFERROR('CALCOLO-Qmedio'!F13,NA()),NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L9" s="35" t="e">
+        <f>IF(DATI_INPUT!D16="MC",IFERROR('CALCOLO-Qmedio'!G13,NA()),NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="M9" s="35" t="e">
+        <f>IF(DATI_INPUT!D16="MC",IFERROR('CALCOLO-Qminimo'!F13,NA()),NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="N9" s="35" t="e">
+        <f>IF(DATI_INPUT!D16="MC",IFERROR('CALCOLO-Qminimo'!G13,NA()),NA())</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E10">
+        <v>2.0074999999999998</v>
+      </c>
+      <c r="F10">
+        <v>0.25209999999999999</v>
+      </c>
+      <c r="I10" s="30">
+        <f>IF(DATI_INPUT!D17="MC",DATI_INPUT!A17,NA())</f>
+        <v>5</v>
+      </c>
+      <c r="J10" s="31">
+        <f>IF(DATI_INPUT!D17="MC",DATI_INPUT!B17,NA())</f>
+        <v>0</v>
+      </c>
+      <c r="K10" s="32">
+        <f>IF(DATI_INPUT!D17="MC",IFERROR('CALCOLO-Qmedio'!F14,NA()),NA())</f>
+        <v>5</v>
+      </c>
+      <c r="L10" s="32" t="str">
+        <f ca="1">IF(DATI_INPUT!D17="MC",IFERROR('CALCOLO-Qmedio'!G14,NA()),NA())</f>
+        <v/>
+      </c>
+      <c r="M10" s="32">
+        <f>IF(DATI_INPUT!D17="MC",IFERROR('CALCOLO-Qminimo'!F14,NA()),NA())</f>
+        <v>6</v>
+      </c>
+      <c r="N10" s="32" t="str">
+        <f ca="1">IF(DATI_INPUT!D17="MC",IFERROR('CALCOLO-Qminimo'!G14,NA()),NA())</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E11">
+        <v>1.9451000000000001</v>
+      </c>
+      <c r="F11">
+        <v>0.22339999999999999</v>
+      </c>
+      <c r="I11" s="33">
+        <f>IF(DATI_INPUT!D18="MC",DATI_INPUT!A18,NA())</f>
+        <v>6</v>
+      </c>
+      <c r="J11" s="34">
+        <f>IF(DATI_INPUT!D18="MC",DATI_INPUT!B18,NA())</f>
+        <v>0</v>
+      </c>
+      <c r="K11" s="35">
+        <f>IF(DATI_INPUT!D18="MC",IFERROR('CALCOLO-Qmedio'!F15,NA()),NA())</f>
+        <v>0</v>
+      </c>
+      <c r="L11" s="35" t="str">
+        <f>IF(DATI_INPUT!D18="MC",IFERROR('CALCOLO-Qmedio'!G15,NA()),NA())</f>
+        <v/>
+      </c>
+      <c r="M11" s="35">
+        <f>IF(DATI_INPUT!D18="MC",IFERROR('CALCOLO-Qminimo'!F15,NA()),NA())</f>
+        <v>0</v>
+      </c>
+      <c r="N11" s="35" t="str">
+        <f>IF(DATI_INPUT!D18="MC",IFERROR('CALCOLO-Qminimo'!G15,NA()),NA())</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E12">
+        <v>2.0882000000000001</v>
+      </c>
+      <c r="F12">
+        <v>0.22520000000000001</v>
+      </c>
+      <c r="I12" s="30" t="e">
+        <f>IF(DATI_INPUT!D19="MC",DATI_INPUT!A19,NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J12" s="31" t="e">
+        <f>IF(DATI_INPUT!D19="MC",DATI_INPUT!B19,NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K12" s="32" t="e">
+        <f>IF(DATI_INPUT!D19="MC",IFERROR('CALCOLO-Qmedio'!F16,NA()),NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L12" s="32" t="e">
+        <f>IF(DATI_INPUT!D19="MC",IFERROR('CALCOLO-Qmedio'!G16,NA()),NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="M12" s="32" t="e">
+        <f>IF(DATI_INPUT!D19="MC",IFERROR('CALCOLO-Qminimo'!F16,NA()),NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="N12" s="32" t="e">
+        <f>IF(DATI_INPUT!D19="MC",IFERROR('CALCOLO-Qminimo'!G16,NA()),NA())</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E13">
+        <v>2.0257999999999998</v>
+      </c>
+      <c r="F13">
+        <v>0.29680000000000001</v>
+      </c>
+      <c r="I13" s="33" t="e">
+        <f>IF(DATI_INPUT!D20="MC",DATI_INPUT!A20,NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J13" s="34" t="e">
+        <f>IF(DATI_INPUT!D20="MC",DATI_INPUT!B20,NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K13" s="35" t="e">
+        <f>IF(DATI_INPUT!D20="MC",IFERROR('CALCOLO-Qmedio'!F17,NA()),NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L13" s="35" t="e">
+        <f>IF(DATI_INPUT!D20="MC",IFERROR('CALCOLO-Qmedio'!G17,NA()),NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="M13" s="35" t="e">
+        <f>IF(DATI_INPUT!D20="MC",IFERROR('CALCOLO-Qminimo'!F17,NA()),NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="N13" s="35" t="e">
+        <f>IF(DATI_INPUT!D20="MC",IFERROR('CALCOLO-Qminimo'!G17,NA()),NA())</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E14">
+        <v>2.4916999999999998</v>
+      </c>
+      <c r="F14">
+        <v>0.24399999999999999</v>
+      </c>
+      <c r="I14" s="30" t="e">
+        <f>IF(DATI_INPUT!D21="MC",DATI_INPUT!A21,NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J14" s="31" t="e">
+        <f>IF(DATI_INPUT!D21="MC",DATI_INPUT!B21,NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K14" s="32" t="e">
+        <f>IF(DATI_INPUT!D21="MC",IFERROR('CALCOLO-Qmedio'!F18,NA()),NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L14" s="32" t="e">
+        <f>IF(DATI_INPUT!D21="MC",IFERROR('CALCOLO-Qmedio'!G18,NA()),NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="M14" s="32" t="e">
+        <f>IF(DATI_INPUT!D21="MC",IFERROR('CALCOLO-Qminimo'!F18,NA()),NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="N14" s="32" t="e">
+        <f>IF(DATI_INPUT!D21="MC",IFERROR('CALCOLO-Qminimo'!G18,NA()),NA())</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E15">
+        <v>2.4990000000000001</v>
+      </c>
+      <c r="F15">
+        <v>0.19570000000000001</v>
+      </c>
+      <c r="I15" s="33" t="e">
+        <f>IF(DATI_INPUT!D22="MC",DATI_INPUT!A22,NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J15" s="34" t="e">
+        <f>IF(DATI_INPUT!D22="MC",DATI_INPUT!B22,NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K15" s="35" t="e">
+        <f>IF(DATI_INPUT!D22="MC",IFERROR('CALCOLO-Qmedio'!F19,NA()),NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L15" s="35" t="e">
+        <f>IF(DATI_INPUT!D22="MC",IFERROR('CALCOLO-Qmedio'!G19,NA()),NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="M15" s="35" t="e">
+        <f>IF(DATI_INPUT!D22="MC",IFERROR('CALCOLO-Qminimo'!F19,NA()),NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="N15" s="35" t="e">
+        <f>IF(DATI_INPUT!D22="MC",IFERROR('CALCOLO-Qminimo'!G19,NA()),NA())</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E16">
+        <v>3.0125999999999999</v>
+      </c>
+      <c r="F16">
+        <v>0.29499999999999998</v>
+      </c>
+    </row>
+    <row r="17" spans="5:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E17">
+        <v>3.3134999999999999</v>
+      </c>
+      <c r="F17">
+        <v>0.29859999999999998</v>
+      </c>
+    </row>
+    <row r="18" spans="5:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E18">
+        <v>3.5886</v>
+      </c>
+      <c r="F18">
+        <v>0.30220000000000002</v>
+      </c>
+    </row>
+    <row r="19" spans="5:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E19">
+        <v>3.6802999999999999</v>
+      </c>
+      <c r="F19">
+        <v>0.3004</v>
+      </c>
+    </row>
+    <row r="20" spans="5:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E20">
+        <v>4.0178000000000003</v>
+      </c>
+      <c r="F20">
+        <v>0.43109999999999998</v>
+      </c>
+    </row>
+    <row r="21" spans="5:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E21">
+        <v>5.0193000000000003</v>
+      </c>
+      <c r="F21">
+        <v>0.432</v>
+      </c>
+    </row>
+    <row r="22" spans="5:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E22">
+        <v>6.0098000000000003</v>
+      </c>
+      <c r="F22">
+        <v>0.44450000000000001</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A2:N2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <sheetPr codeName="Foglio9"/>
   <dimension ref="A1:N24"/>
@@ -7284,100 +8046,100 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="56" t="s">
+        <v>100</v>
+      </c>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="56"/>
+      <c r="J1" s="56"/>
+      <c r="K1" s="56"/>
+      <c r="L1" s="56"/>
+      <c r="M1" s="56"/>
+      <c r="N1" s="56"/>
+    </row>
+    <row r="2" spans="1:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="53" t="s">
         <v>101</v>
       </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
-      <c r="F1" s="46"/>
-      <c r="G1" s="46"/>
-      <c r="H1" s="46"/>
-      <c r="I1" s="46"/>
-      <c r="J1" s="46"/>
-      <c r="K1" s="46"/>
-      <c r="L1" s="46"/>
-      <c r="M1" s="46"/>
-      <c r="N1" s="46"/>
-    </row>
-    <row r="2" spans="1:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="50" t="s">
-        <v>102</v>
-      </c>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="50"/>
-      <c r="H2" s="50"/>
-      <c r="I2" s="50"/>
-      <c r="J2" s="50"/>
-      <c r="K2" s="50"/>
-      <c r="L2" s="50"/>
-      <c r="M2" s="50"/>
-      <c r="N2" s="50"/>
+      <c r="B2" s="53"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="53"/>
+      <c r="L2" s="53"/>
+      <c r="M2" s="53"/>
+      <c r="N2" s="53"/>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="26" t="s">
+        <v>102</v>
+      </c>
+      <c r="C4" s="26" t="s">
         <v>103</v>
       </c>
-      <c r="C4" s="26" t="s">
-        <v>104</v>
-      </c>
       <c r="E4" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="G4" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="G4" s="26" t="s">
+      <c r="I4" s="27" t="s">
         <v>87</v>
-      </c>
-      <c r="I4" s="27" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="28" t="s">
+        <v>88</v>
+      </c>
+      <c r="B5" s="28" t="s">
         <v>89</v>
       </c>
-      <c r="B5" s="28" t="s">
+      <c r="C5" s="28" t="s">
+        <v>88</v>
+      </c>
+      <c r="D5" s="28" t="s">
+        <v>89</v>
+      </c>
+      <c r="E5" s="28" t="s">
+        <v>88</v>
+      </c>
+      <c r="F5" s="28" t="s">
+        <v>89</v>
+      </c>
+      <c r="G5" s="28" t="s">
+        <v>88</v>
+      </c>
+      <c r="H5" s="28" t="s">
+        <v>89</v>
+      </c>
+      <c r="I5" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="J5" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="K5" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="L5" s="29" t="s">
         <v>90</v>
       </c>
-      <c r="C5" s="28" t="s">
-        <v>89</v>
-      </c>
-      <c r="D5" s="28" t="s">
-        <v>90</v>
-      </c>
-      <c r="E5" s="28" t="s">
-        <v>89</v>
-      </c>
-      <c r="F5" s="28" t="s">
-        <v>90</v>
-      </c>
-      <c r="G5" s="28" t="s">
-        <v>89</v>
-      </c>
-      <c r="H5" s="28" t="s">
-        <v>90</v>
-      </c>
-      <c r="I5" s="29" t="s">
-        <v>24</v>
-      </c>
-      <c r="J5" s="29" t="s">
-        <v>25</v>
-      </c>
-      <c r="K5" s="29" t="s">
+      <c r="M5" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="L5" s="29" t="s">
+      <c r="N5" s="29" t="s">
         <v>91</v>
-      </c>
-      <c r="M5" s="29" t="s">
-        <v>29</v>
-      </c>
-      <c r="N5" s="29" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7695,17 +8457,17 @@
         <f>IF(DATI_INPUT!D20="RA",IFERROR('CALCOLO-Qmedio'!F17,NA()),NA())</f>
         <v>3.5</v>
       </c>
-      <c r="L13" s="35">
-        <f>IF(DATI_INPUT!D20="RA",IFERROR('CALCOLO-Qmedio'!G17,NA()),NA())</f>
-        <v>0.48321706743369969</v>
+      <c r="L13" s="35" t="str">
+        <f ca="1">IF(DATI_INPUT!D20="RA",IFERROR('CALCOLO-Qmedio'!G17,NA()),NA())</f>
+        <v/>
       </c>
       <c r="M13" s="35">
         <f>IF(DATI_INPUT!D20="RA",IFERROR('CALCOLO-Qminimo'!F17,NA()),NA())</f>
         <v>3</v>
       </c>
-      <c r="N13" s="35">
-        <f>IF(DATI_INPUT!D20="RA",IFERROR('CALCOLO-Qminimo'!G17,NA()),NA())</f>
-        <v>0.41883573812024932</v>
+      <c r="N13" s="35" t="str">
+        <f ca="1">IF(DATI_INPUT!D20="RA",IFERROR('CALCOLO-Qminimo'!G17,NA()),NA())</f>
+        <v/>
       </c>
     </row>
     <row r="14" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7868,6 +8630,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38CCF5D4-6705-444B-AE2E-05E6B34F4E4D}">
+  <sheetPr codeName="Foglio10"/>
   <dimension ref="A1:B19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -7876,57 +8639,57 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="53" t="s">
+      <c r="A1" s="59" t="s">
+        <v>104</v>
+      </c>
+      <c r="B1" s="58"/>
+    </row>
+    <row r="2" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="60" t="s">
         <v>105</v>
       </c>
-      <c r="B1" s="52"/>
-    </row>
-    <row r="2" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="54" t="s">
-        <v>106</v>
-      </c>
-      <c r="B2" s="52"/>
+      <c r="B2" s="58"/>
     </row>
     <row r="3" spans="1:2" ht="8.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="41"/>
       <c r="B3" s="41"/>
     </row>
     <row r="4" spans="1:2" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="55" t="s">
-        <v>107</v>
-      </c>
-      <c r="B4" s="52"/>
+      <c r="A4" s="61" t="s">
+        <v>106</v>
+      </c>
+      <c r="B4" s="58"/>
     </row>
     <row r="5" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="42" t="s">
+        <v>107</v>
+      </c>
+      <c r="B5" s="43" t="s">
         <v>108</v>
       </c>
-      <c r="B5" s="43" t="s">
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="42" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="42" t="s">
+      <c r="B6" s="51" t="s">
         <v>110</v>
       </c>
-      <c r="B6" s="44" t="s">
+    </row>
+    <row r="7" spans="1:2" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A7" s="42" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="42" t="s">
+      <c r="B7" s="51" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A8" s="42" t="s">
         <v>112</v>
       </c>
-      <c r="B7" s="44" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="42" t="s">
-        <v>114</v>
-      </c>
-      <c r="B8" s="44" t="s">
-        <v>115</v>
+      <c r="B8" s="51" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="8.1" customHeight="1" x14ac:dyDescent="0.3">
@@ -7934,17 +8697,17 @@
       <c r="B9" s="41"/>
     </row>
     <row r="10" spans="1:2" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="55" t="s">
-        <v>116</v>
-      </c>
-      <c r="B10" s="52"/>
+      <c r="A10" s="61" t="s">
+        <v>113</v>
+      </c>
+      <c r="B10" s="58"/>
     </row>
     <row r="11" spans="1:2" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="42" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B11" s="43" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="8.1" customHeight="1" x14ac:dyDescent="0.3">
@@ -7952,17 +8715,17 @@
       <c r="B12" s="41"/>
     </row>
     <row r="13" spans="1:2" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="55" t="s">
-        <v>119</v>
-      </c>
-      <c r="B13" s="52"/>
+      <c r="A13" s="61" t="s">
+        <v>116</v>
+      </c>
+      <c r="B13" s="58"/>
     </row>
     <row r="14" spans="1:2" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A14" s="42" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B14" s="43" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="8.1" customHeight="1" x14ac:dyDescent="0.3">
@@ -7970,17 +8733,17 @@
       <c r="B15" s="41"/>
     </row>
     <row r="16" spans="1:2" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="55" t="s">
-        <v>122</v>
-      </c>
-      <c r="B16" s="52"/>
+      <c r="A16" s="61" t="s">
+        <v>119</v>
+      </c>
+      <c r="B16" s="58"/>
     </row>
     <row r="17" spans="1:2" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="42" t="s">
-        <v>123</v>
-      </c>
-      <c r="B17" s="45" t="s">
-        <v>124</v>
+        <v>120</v>
+      </c>
+      <c r="B17" s="44" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="8.1" customHeight="1" x14ac:dyDescent="0.3">
@@ -7988,10 +8751,10 @@
       <c r="B18" s="41"/>
     </row>
     <row r="19" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="51" t="s">
-        <v>125</v>
-      </c>
-      <c r="B19" s="52"/>
+      <c r="A19" s="57" t="s">
+        <v>122</v>
+      </c>
+      <c r="B19" s="58"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -8003,7 +8766,13 @@
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="A16:B16"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="B7" r:id="rId1" xr:uid="{C6054F06-768D-423A-9EED-0DC3E01A3219}"/>
+    <hyperlink ref="B6" r:id="rId2" xr:uid="{D4A2242F-92AF-4602-A861-F28EE6A9EE5E}"/>
+    <hyperlink ref="B8" r:id="rId3" xr:uid="{2D020C50-34C3-4628-912C-0CAA5B951D9F}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId4"/>
 </worksheet>
 </file>
 
@@ -8026,203 +8795,203 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="56" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
-      <c r="F1" s="46"/>
-      <c r="G1" s="46"/>
-      <c r="H1" s="46"/>
-      <c r="I1" s="46"/>
-      <c r="J1" s="46"/>
-      <c r="K1" s="46"/>
-      <c r="L1" s="46"/>
-      <c r="M1" s="46"/>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="56"/>
+      <c r="J1" s="56"/>
+      <c r="K1" s="56"/>
+      <c r="L1" s="56"/>
+      <c r="M1" s="56"/>
     </row>
     <row r="3" spans="1:13" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="47" t="s">
+      <c r="A3" s="52" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="47"/>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="47"/>
-      <c r="G3" s="47"/>
-      <c r="H3" s="47"/>
-      <c r="I3" s="47"/>
-      <c r="J3" s="47"/>
-      <c r="K3" s="47"/>
-      <c r="L3" s="47"/>
-      <c r="M3" s="47"/>
+      <c r="B3" s="52"/>
+      <c r="C3" s="52"/>
+      <c r="D3" s="52"/>
+      <c r="E3" s="52"/>
+      <c r="F3" s="52"/>
+      <c r="G3" s="52"/>
+      <c r="H3" s="52"/>
+      <c r="I3" s="52"/>
+      <c r="J3" s="52"/>
+      <c r="K3" s="52"/>
+      <c r="L3" s="52"/>
+      <c r="M3" s="52"/>
     </row>
     <row r="4" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="48" t="s">
+      <c r="A4" s="54" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="48"/>
+      <c r="B4" s="54"/>
       <c r="C4" s="2"/>
     </row>
     <row r="5" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="48" t="s">
+      <c r="A5" s="54" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="48"/>
+      <c r="B5" s="54"/>
       <c r="C5" s="2">
         <v>0.15</v>
       </c>
-      <c r="D5" s="49" t="s">
+      <c r="D5" s="55" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="49"/>
-      <c r="F5" s="49"/>
-      <c r="G5" s="49"/>
-      <c r="H5" s="49"/>
-      <c r="I5" s="49"/>
-      <c r="J5" s="49"/>
-      <c r="K5" s="49"/>
-      <c r="L5" s="49"/>
-      <c r="M5" s="49"/>
+      <c r="E5" s="55"/>
+      <c r="F5" s="55"/>
+      <c r="G5" s="55"/>
+      <c r="H5" s="55"/>
+      <c r="I5" s="55"/>
+      <c r="J5" s="55"/>
+      <c r="K5" s="55"/>
+      <c r="L5" s="55"/>
+      <c r="M5" s="55"/>
     </row>
     <row r="6" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="48" t="s">
+      <c r="A6" s="54" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="48"/>
+      <c r="B6" s="54"/>
       <c r="C6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="49" t="s">
+      <c r="D6" s="55" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="49"/>
-      <c r="F6" s="49"/>
-      <c r="G6" s="49"/>
-      <c r="H6" s="49"/>
-      <c r="I6" s="49"/>
-      <c r="J6" s="49"/>
-      <c r="K6" s="49"/>
-      <c r="L6" s="49"/>
-      <c r="M6" s="49"/>
+      <c r="E6" s="55"/>
+      <c r="F6" s="55"/>
+      <c r="G6" s="55"/>
+      <c r="H6" s="55"/>
+      <c r="I6" s="55"/>
+      <c r="J6" s="55"/>
+      <c r="K6" s="55"/>
+      <c r="L6" s="55"/>
+      <c r="M6" s="55"/>
     </row>
     <row r="7" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="48" t="s">
+      <c r="A7" s="54" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="48"/>
+      <c r="B7" s="54"/>
       <c r="C7" s="2">
         <v>3</v>
       </c>
-      <c r="D7" s="49" t="s">
+      <c r="D7" s="55" t="s">
         <v>19</v>
       </c>
-      <c r="E7" s="49"/>
-      <c r="F7" s="49"/>
-      <c r="G7" s="49"/>
-      <c r="H7" s="49"/>
-      <c r="I7" s="49"/>
-      <c r="J7" s="49"/>
-      <c r="K7" s="49"/>
-      <c r="L7" s="49"/>
-      <c r="M7" s="49"/>
+      <c r="E7" s="55"/>
+      <c r="F7" s="55"/>
+      <c r="G7" s="55"/>
+      <c r="H7" s="55"/>
+      <c r="I7" s="55"/>
+      <c r="J7" s="55"/>
+      <c r="K7" s="55"/>
+      <c r="L7" s="55"/>
+      <c r="M7" s="55"/>
     </row>
     <row r="8" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="48" t="s">
+      <c r="A8" s="54" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="48"/>
+      <c r="B8" s="54"/>
       <c r="C8" s="2">
         <v>1</v>
       </c>
-      <c r="D8" s="49" t="s">
+      <c r="D8" s="55" t="s">
         <v>21</v>
       </c>
-      <c r="E8" s="49"/>
-      <c r="F8" s="49"/>
-      <c r="G8" s="49"/>
-      <c r="H8" s="49"/>
-      <c r="I8" s="49"/>
-      <c r="J8" s="49"/>
-      <c r="K8" s="49"/>
-      <c r="L8" s="49"/>
-      <c r="M8" s="49"/>
+      <c r="E8" s="55"/>
+      <c r="F8" s="55"/>
+      <c r="G8" s="55"/>
+      <c r="H8" s="55"/>
+      <c r="I8" s="55"/>
+      <c r="J8" s="55"/>
+      <c r="K8" s="55"/>
+      <c r="L8" s="55"/>
+      <c r="M8" s="55"/>
     </row>
     <row r="10" spans="1:13" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="47" t="s">
+      <c r="A10" s="52" t="s">
         <v>22</v>
       </c>
-      <c r="B10" s="47"/>
-      <c r="C10" s="47"/>
-      <c r="D10" s="47"/>
-      <c r="E10" s="47"/>
-      <c r="F10" s="47"/>
-      <c r="G10" s="47"/>
-      <c r="H10" s="47"/>
-      <c r="I10" s="47"/>
-      <c r="J10" s="47"/>
-      <c r="K10" s="47"/>
-      <c r="L10" s="47"/>
-      <c r="M10" s="47"/>
+      <c r="B10" s="52"/>
+      <c r="C10" s="52"/>
+      <c r="D10" s="52"/>
+      <c r="E10" s="52"/>
+      <c r="F10" s="52"/>
+      <c r="G10" s="52"/>
+      <c r="H10" s="52"/>
+      <c r="I10" s="52"/>
+      <c r="J10" s="52"/>
+      <c r="K10" s="52"/>
+      <c r="L10" s="52"/>
+      <c r="M10" s="52"/>
     </row>
     <row r="11" spans="1:13" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="50" t="s">
-        <v>23</v>
-      </c>
-      <c r="B11" s="50"/>
-      <c r="C11" s="50"/>
-      <c r="D11" s="50"/>
-      <c r="E11" s="50"/>
-      <c r="F11" s="50"/>
-      <c r="G11" s="50"/>
-      <c r="H11" s="50"/>
-      <c r="I11" s="50"/>
-      <c r="J11" s="50"/>
-      <c r="K11" s="50"/>
-      <c r="L11" s="50"/>
-      <c r="M11" s="50"/>
+      <c r="A11" s="53" t="s">
+        <v>160</v>
+      </c>
+      <c r="B11" s="53"/>
+      <c r="C11" s="53"/>
+      <c r="D11" s="53"/>
+      <c r="E11" s="53"/>
+      <c r="F11" s="53"/>
+      <c r="G11" s="53"/>
+      <c r="H11" s="53"/>
+      <c r="I11" s="53"/>
+      <c r="J11" s="53"/>
+      <c r="K11" s="53"/>
+      <c r="L11" s="53"/>
+      <c r="M11" s="53"/>
     </row>
     <row r="12" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="C12" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="D12" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="E12" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="F12" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F12" s="3" t="s">
+      <c r="G12" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="G12" s="3" t="s">
+      <c r="H12" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="H12" s="3" t="s">
+      <c r="I12" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="I12" s="3" t="s">
+      <c r="J12" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="J12" s="3" t="s">
+      <c r="K12" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="K12" s="3" t="s">
+      <c r="L12" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="L12" s="3" t="s">
+      <c r="M12" s="3" t="s">
         <v>35</v>
-      </c>
-      <c r="M12" s="3" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8245,11 +9014,11 @@
         <v>15</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="J13" s="5">
-        <f>IFERROR(getalpha(D13,DATI_INPUT!C6),"–")</f>
-        <v>1.7</v>
+        <v>36</v>
+      </c>
+      <c r="J13" s="5" t="str">
+        <f ca="1">IFERROR(getalpha(D13,DATI_INPUT!C6),"–")</f>
+        <v>–</v>
       </c>
       <c r="K13" s="6" t="str">
         <f ca="1">IFERROR(getvi_min(D13,DATI_INPUT!C6,PI()*(getalpha(D13,DATI_INPUT!C6)*DATI_INPUT!C5)^2/4*C13),"–")</f>
@@ -8280,11 +9049,11 @@
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
       <c r="I14" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="J14" s="8">
-        <f>IFERROR(getalpha(D14,DATI_INPUT!C6),"–")</f>
-        <v>1.7</v>
+        <v>36</v>
+      </c>
+      <c r="J14" s="8" t="str">
+        <f ca="1">IFERROR(getalpha(D14,DATI_INPUT!C6),"–")</f>
+        <v>–</v>
       </c>
       <c r="K14" s="9" t="str">
         <f ca="1">IFERROR(getvi_min(D14,DATI_INPUT!C6,PI()*(getalpha(D14,DATI_INPUT!C6)*DATI_INPUT!C5)^2/4*C14),"–")</f>
@@ -8315,15 +9084,15 @@
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
       <c r="I15" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="J15" s="5">
-        <f>IFERROR(getalpha(D15,DATI_INPUT!C6),"–")</f>
-        <v>1.8</v>
-      </c>
-      <c r="K15" s="6">
-        <f>IFERROR(getvi_min(D15,DATI_INPUT!C6,PI()*(getalpha(D15,DATI_INPUT!C6)*DATI_INPUT!C5)^2/4*C15),"–")</f>
-        <v>0.17176657833502196</v>
+        <v>36</v>
+      </c>
+      <c r="J15" s="5" t="str">
+        <f ca="1">IFERROR(getalpha(D15,DATI_INPUT!C6),"–")</f>
+        <v>–</v>
+      </c>
+      <c r="K15" s="6" t="str">
+        <f ca="1">IFERROR(getvi_min(D15,DATI_INPUT!C6,PI()*(getalpha(D15,DATI_INPUT!C6)*DATI_INPUT!C5)^2/4*C15),"–")</f>
+        <v>–</v>
       </c>
       <c r="L15" s="2">
         <v>1.8</v>
@@ -8350,11 +9119,11 @@
         <v>20</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="J16" s="8">
-        <f>IFERROR(getalpha(D16,DATI_INPUT!C6),"–")</f>
-        <v>1.8</v>
+        <v>123</v>
+      </c>
+      <c r="J16" s="8" t="str">
+        <f ca="1">IFERROR(getalpha(D16,DATI_INPUT!C6),"–")</f>
+        <v>–</v>
       </c>
       <c r="K16" s="9" t="str">
         <f ca="1">IFERROR(getvi_min(D16,DATI_INPUT!C6,PI()*(getalpha(D16,DATI_INPUT!C6)*DATI_INPUT!C5)^2/4*C16),"–")</f>
@@ -8385,11 +9154,11 @@
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
       <c r="I17" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="J17" s="5">
-        <f>IFERROR(getalpha(D17,DATI_INPUT!C6),"–")</f>
-        <v>1.8</v>
+        <v>36</v>
+      </c>
+      <c r="J17" s="5" t="str">
+        <f ca="1">IFERROR(getalpha(D17,DATI_INPUT!C6),"–")</f>
+        <v>–</v>
       </c>
       <c r="K17" s="6" t="str">
         <f ca="1">IFERROR(getvi_min(D17,DATI_INPUT!C6,PI()*(getalpha(D17,DATI_INPUT!C6)*DATI_INPUT!C5)^2/4*C17),"–")</f>
@@ -8420,15 +9189,15 @@
         <v>80</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="J18" s="8">
-        <f>IFERROR(getalpha(D18,DATI_INPUT!C6),"–")</f>
-        <v>1.8</v>
-      </c>
-      <c r="K18" s="9">
-        <f>IFERROR(getvi_min(D18,DATI_INPUT!C6,PI()*(getalpha(D18,DATI_INPUT!C6)*DATI_INPUT!C5)^2/4*C18),"–")</f>
-        <v>0.20039434139085893</v>
+        <v>36</v>
+      </c>
+      <c r="J18" s="8" t="str">
+        <f ca="1">IFERROR(getalpha(D18,DATI_INPUT!C6),"–")</f>
+        <v>–</v>
+      </c>
+      <c r="K18" s="9" t="str">
+        <f ca="1">IFERROR(getvi_min(D18,DATI_INPUT!C6,PI()*(getalpha(D18,DATI_INPUT!C6)*DATI_INPUT!C5)^2/4*C18),"–")</f>
+        <v>–</v>
       </c>
       <c r="L18" s="2">
         <v>1.5</v>
@@ -8455,11 +9224,11 @@
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
       <c r="I19" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="J19" s="5">
-        <f>IFERROR(getalpha(D19,DATI_INPUT!C6),"–")</f>
-        <v>1.2</v>
+        <v>36</v>
+      </c>
+      <c r="J19" s="5" t="str">
+        <f ca="1">IFERROR(getalpha(D19,DATI_INPUT!C6),"–")</f>
+        <v>–</v>
       </c>
       <c r="K19" s="6" t="str">
         <f ca="1">IFERROR(getvi_min(D19,DATI_INPUT!C6,PI()*(getalpha(D19,DATI_INPUT!C6)*DATI_INPUT!C5)^2/4*C19),"–")</f>
@@ -8490,15 +9259,15 @@
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
       <c r="I20" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="J20" s="8">
-        <f>IFERROR(getalpha(D20,DATI_INPUT!C6),"–")</f>
-        <v>1.2</v>
-      </c>
-      <c r="K20" s="9">
-        <f>IFERROR(getvi_min(D20,DATI_INPUT!C6,PI()*(getalpha(D20,DATI_INPUT!C6)*DATI_INPUT!C5)^2/4*C20),"–")</f>
-        <v>6.6161941284601039E-2</v>
+        <v>36</v>
+      </c>
+      <c r="J20" s="8" t="str">
+        <f ca="1">IFERROR(getalpha(D20,DATI_INPUT!C6),"–")</f>
+        <v>–</v>
+      </c>
+      <c r="K20" s="9" t="str">
+        <f ca="1">IFERROR(getvi_min(D20,DATI_INPUT!C6,PI()*(getalpha(D20,DATI_INPUT!C6)*DATI_INPUT!C5)^2/4*C20),"–")</f>
+        <v>–</v>
       </c>
       <c r="L20" s="2">
         <v>1.5</v>
@@ -8517,7 +9286,7 @@
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
       <c r="I21" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J21" s="5" t="str">
         <f ca="1">IFERROR(getalpha(D21,DATI_INPUT!C6),"–")</f>
@@ -8544,7 +9313,7 @@
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
       <c r="I22" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J22" s="8" t="str">
         <f ca="1">IFERROR(getalpha(D22,DATI_INPUT!C6),"–")</f>
@@ -8561,6 +9330,11 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A3:M3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="D5:M5"/>
     <mergeCell ref="A10:M10"/>
     <mergeCell ref="A11:M11"/>
     <mergeCell ref="A6:B6"/>
@@ -8569,11 +9343,6 @@
     <mergeCell ref="D7:M7"/>
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="D8:M8"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="A3:M3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="D5:M5"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" sqref="C6" xr:uid="{00000000-0002-0000-0100-000000000000}">
@@ -8590,11 +9359,266 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="61" fitToHeight="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="92" fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8193967E-A0C2-4A23-8EF9-AEFA00501C57}">
+  <sheetPr codeName="Foglio11">
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:D20"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="30" style="45" customWidth="1"/>
+    <col min="2" max="3" width="16" style="45" customWidth="1"/>
+    <col min="4" max="4" width="44" style="45" customWidth="1"/>
+    <col min="5" max="16384" width="9.140625" style="45"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="64" t="s">
+        <v>124</v>
+      </c>
+      <c r="B1" s="63"/>
+      <c r="C1" s="63"/>
+      <c r="D1" s="63"/>
+    </row>
+    <row r="2" spans="1:4" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:4" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="65" t="s">
+        <v>125</v>
+      </c>
+      <c r="B3" s="65" t="s">
+        <v>126</v>
+      </c>
+      <c r="C3" s="63"/>
+      <c r="D3" s="65" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="63"/>
+      <c r="B4" s="46" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="46" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="63"/>
+    </row>
+    <row r="5" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="47" t="s">
+        <v>128</v>
+      </c>
+      <c r="B5" s="48" t="s">
+        <v>129</v>
+      </c>
+      <c r="C5" s="48" t="s">
+        <v>130</v>
+      </c>
+      <c r="D5" s="47" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="49" t="s">
+        <v>132</v>
+      </c>
+      <c r="B6" s="50" t="s">
+        <v>133</v>
+      </c>
+      <c r="C6" s="50" t="s">
+        <v>130</v>
+      </c>
+      <c r="D6" s="49" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="47" t="s">
+        <v>134</v>
+      </c>
+      <c r="B7" s="48" t="s">
+        <v>135</v>
+      </c>
+      <c r="C7" s="48" t="s">
+        <v>136</v>
+      </c>
+      <c r="D7" s="47" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="49" t="s">
+        <v>137</v>
+      </c>
+      <c r="B8" s="50" t="s">
+        <v>138</v>
+      </c>
+      <c r="C8" s="50" t="s">
+        <v>139</v>
+      </c>
+      <c r="D8" s="49" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="47" t="s">
+        <v>140</v>
+      </c>
+      <c r="B9" s="48" t="s">
+        <v>138</v>
+      </c>
+      <c r="C9" s="48" t="s">
+        <v>139</v>
+      </c>
+      <c r="D9" s="47" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="49" t="s">
+        <v>141</v>
+      </c>
+      <c r="B10" s="50" t="s">
+        <v>138</v>
+      </c>
+      <c r="C10" s="50" t="s">
+        <v>139</v>
+      </c>
+      <c r="D10" s="49" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="47" t="s">
+        <v>142</v>
+      </c>
+      <c r="B11" s="48" t="s">
+        <v>138</v>
+      </c>
+      <c r="C11" s="48" t="s">
+        <v>139</v>
+      </c>
+      <c r="D11" s="47" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="49" t="s">
+        <v>144</v>
+      </c>
+      <c r="B12" s="50" t="s">
+        <v>145</v>
+      </c>
+      <c r="C12" s="50" t="s">
+        <v>139</v>
+      </c>
+      <c r="D12" s="49" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="47" t="s">
+        <v>147</v>
+      </c>
+      <c r="B13" s="48" t="s">
+        <v>148</v>
+      </c>
+      <c r="C13" s="48" t="s">
+        <v>149</v>
+      </c>
+      <c r="D13" s="47" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="49" t="s">
+        <v>151</v>
+      </c>
+      <c r="B14" s="50" t="s">
+        <v>129</v>
+      </c>
+      <c r="C14" s="50" t="s">
+        <v>139</v>
+      </c>
+      <c r="D14" s="66" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="47" t="s">
+        <v>153</v>
+      </c>
+      <c r="B15" s="48" t="s">
+        <v>129</v>
+      </c>
+      <c r="C15" s="48" t="s">
+        <v>139</v>
+      </c>
+      <c r="D15" s="63"/>
+    </row>
+    <row r="16" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="49" t="s">
+        <v>154</v>
+      </c>
+      <c r="B16" s="50" t="s">
+        <v>129</v>
+      </c>
+      <c r="C16" s="50" t="s">
+        <v>139</v>
+      </c>
+      <c r="D16" s="63"/>
+    </row>
+    <row r="17" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="47" t="s">
+        <v>155</v>
+      </c>
+      <c r="B17" s="48" t="s">
+        <v>149</v>
+      </c>
+      <c r="C17" s="48" t="s">
+        <v>156</v>
+      </c>
+      <c r="D17" s="47" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="62" t="s">
+        <v>158</v>
+      </c>
+      <c r="B19" s="63"/>
+      <c r="C19" s="63"/>
+      <c r="D19" s="63"/>
+    </row>
+    <row r="20" spans="1:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="62" t="s">
+        <v>159</v>
+      </c>
+      <c r="B20" s="63"/>
+      <c r="C20" s="63"/>
+      <c r="D20" s="63"/>
+    </row>
+  </sheetData>
+  <sheetProtection password="CE4B" sheet="1"/>
+  <mergeCells count="7">
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="D14:D16"/>
+    <mergeCell ref="A19:D19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" scale="81" fitToHeight="0" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Foglio3">
     <pageSetUpPr fitToPage="1"/>
@@ -8611,103 +9635,103 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="56" t="s">
+      <c r="A1" s="72" t="s">
+        <v>37</v>
+      </c>
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
+      <c r="E1" s="72"/>
+      <c r="F1" s="72"/>
+      <c r="G1" s="72"/>
+      <c r="H1" s="72"/>
+    </row>
+    <row r="2" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="53" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-    </row>
-    <row r="2" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="50" t="s">
+      <c r="B2" s="53"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+    </row>
+    <row r="4" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="52" t="s">
         <v>39</v>
       </c>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="50"/>
-      <c r="H2" s="50"/>
-    </row>
-    <row r="4" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="47" t="s">
+      <c r="B4" s="52"/>
+      <c r="C4" s="52"/>
+      <c r="D4" s="52"/>
+      <c r="E4" s="52"/>
+      <c r="F4" s="52"/>
+      <c r="G4" s="52"/>
+      <c r="H4" s="52"/>
+    </row>
+    <row r="5" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="67" t="s">
         <v>40</v>
       </c>
-      <c r="B4" s="47"/>
-      <c r="C4" s="47"/>
-      <c r="D4" s="47"/>
-      <c r="E4" s="47"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="47"/>
-      <c r="H4" s="47"/>
-    </row>
-    <row r="5" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="57" t="s">
-        <v>41</v>
-      </c>
-      <c r="B5" s="57"/>
-      <c r="C5" s="57"/>
+      <c r="B5" s="67"/>
+      <c r="C5" s="67"/>
       <c r="D5" s="4">
         <f>DATI_INPUT!C5</f>
         <v>0.15</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="57" t="s">
-        <v>42</v>
-      </c>
-      <c r="B6" s="57"/>
-      <c r="C6" s="57"/>
+      <c r="A6" s="67" t="s">
+        <v>41</v>
+      </c>
+      <c r="B6" s="67"/>
+      <c r="C6" s="67"/>
       <c r="D6" s="4" t="str">
         <f>DATI_INPUT!C6</f>
         <v>IRS</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="57" t="s">
-        <v>43</v>
-      </c>
-      <c r="B7" s="57"/>
-      <c r="C7" s="57"/>
+      <c r="A7" s="67" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7" s="67"/>
+      <c r="C7" s="67"/>
       <c r="D7" s="2">
         <v>0.15</v>
       </c>
-      <c r="E7" s="58" t="s">
-        <v>44</v>
-      </c>
-      <c r="F7" s="58"/>
-      <c r="G7" s="58"/>
-      <c r="H7" s="58"/>
+      <c r="E7" s="68" t="s">
+        <v>43</v>
+      </c>
+      <c r="F7" s="68"/>
+      <c r="G7" s="68"/>
+      <c r="H7" s="68"/>
     </row>
     <row r="9" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="10" t="s">
+      <c r="C9" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="10" t="s">
-        <v>26</v>
-      </c>
       <c r="D9" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="E9" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="E9" s="10" t="s">
+      <c r="F9" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="F9" s="10" t="s">
+      <c r="G9" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="G9" s="10" t="s">
+      <c r="H9" s="10" t="s">
         <v>48</v>
-      </c>
-      <c r="H9" s="10" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8965,13 +9989,13 @@
         <f>IFERROR(IF(DATI_INPUT!I20="Sì",getpl_fromnspt(DATI_INPUT!D20,DATI_INPUT!G20),IF(DATI_INPUT!E20="",0,DATI_INPUT!E20)),IF(DATI_INPUT!E20="",0,DATI_INPUT!E20))</f>
         <v>3.5</v>
       </c>
-      <c r="G17" s="14">
-        <f>IFERROR(IF(OR(C17="",F17=0),"",getqs(DATI_INPUT!D20,DATI_INPUT!C6,F17)),"")</f>
-        <v>0.48321706743369969</v>
+      <c r="G17" s="14" t="str">
+        <f ca="1">IFERROR(IF(OR(C17="",F17=0),"",getqs(DATI_INPUT!D20,DATI_INPUT!C6,F17)),"")</f>
+        <v/>
       </c>
       <c r="H17" s="15">
-        <f t="shared" si="0"/>
-        <v>683.1320351125114</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9041,69 +10065,69 @@
       </c>
     </row>
     <row r="20" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="59" t="s">
-        <v>50</v>
-      </c>
-      <c r="B20" s="59"/>
-      <c r="C20" s="59"/>
-      <c r="D20" s="59"/>
-      <c r="E20" s="59"/>
-      <c r="F20" s="59"/>
-      <c r="G20" s="59"/>
+      <c r="A20" s="69" t="s">
+        <v>49</v>
+      </c>
+      <c r="B20" s="69"/>
+      <c r="C20" s="69"/>
+      <c r="D20" s="69"/>
+      <c r="E20" s="69"/>
+      <c r="F20" s="69"/>
+      <c r="G20" s="69"/>
       <c r="H20" s="16">
         <f ca="1">SUM(H10:H19)</f>
-        <v>683.1320351125114</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="60" t="s">
-        <v>51</v>
-      </c>
-      <c r="B21" s="60"/>
-      <c r="C21" s="60"/>
-      <c r="D21" s="60"/>
-      <c r="E21" s="60"/>
-      <c r="F21" s="60"/>
-      <c r="G21" s="60"/>
+      <c r="A21" s="70" t="s">
+        <v>50</v>
+      </c>
+      <c r="B21" s="70"/>
+      <c r="C21" s="70"/>
+      <c r="D21" s="70"/>
+      <c r="E21" s="70"/>
+      <c r="F21" s="70"/>
+      <c r="G21" s="70"/>
       <c r="H21" s="15">
         <f ca="1">D7*H20</f>
-        <v>102.4698052668767</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="61" t="s">
-        <v>52</v>
-      </c>
-      <c r="B22" s="61"/>
-      <c r="C22" s="61"/>
-      <c r="D22" s="61"/>
-      <c r="E22" s="61"/>
-      <c r="F22" s="61"/>
-      <c r="G22" s="61"/>
+      <c r="A22" s="71" t="s">
+        <v>51</v>
+      </c>
+      <c r="B22" s="71"/>
+      <c r="C22" s="71"/>
+      <c r="D22" s="71"/>
+      <c r="E22" s="71"/>
+      <c r="F22" s="71"/>
+      <c r="G22" s="71"/>
       <c r="H22" s="16">
         <f ca="1">H20+H21</f>
-        <v>785.60184037938814</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A6:C6"/>
     <mergeCell ref="A7:C7"/>
     <mergeCell ref="E7:H7"/>
     <mergeCell ref="A20:G20"/>
     <mergeCell ref="A21:G21"/>
     <mergeCell ref="A22:G22"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A6:C6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="95" fitToHeight="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Foglio4">
     <pageSetUpPr fitToPage="1"/>
@@ -9120,103 +10144,103 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
-      <c r="F1" s="46"/>
-      <c r="G1" s="46"/>
-      <c r="H1" s="46"/>
+      <c r="A1" s="56" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
     </row>
     <row r="2" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="50" t="s">
+      <c r="A2" s="53" t="s">
+        <v>38</v>
+      </c>
+      <c r="B2" s="53"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+    </row>
+    <row r="4" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="77" t="s">
         <v>39</v>
       </c>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="50"/>
-      <c r="H2" s="50"/>
-    </row>
-    <row r="4" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="62" t="s">
+      <c r="B4" s="77"/>
+      <c r="C4" s="77"/>
+      <c r="D4" s="77"/>
+      <c r="E4" s="77"/>
+      <c r="F4" s="77"/>
+      <c r="G4" s="77"/>
+      <c r="H4" s="77"/>
+    </row>
+    <row r="5" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="73" t="s">
         <v>40</v>
       </c>
-      <c r="B4" s="62"/>
-      <c r="C4" s="62"/>
-      <c r="D4" s="62"/>
-      <c r="E4" s="62"/>
-      <c r="F4" s="62"/>
-      <c r="G4" s="62"/>
-      <c r="H4" s="62"/>
-    </row>
-    <row r="5" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="63" t="s">
-        <v>41</v>
-      </c>
-      <c r="B5" s="63"/>
-      <c r="C5" s="63"/>
+      <c r="B5" s="73"/>
+      <c r="C5" s="73"/>
       <c r="D5" s="4">
         <f>DATI_INPUT!C5</f>
         <v>0.15</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="63" t="s">
-        <v>42</v>
-      </c>
-      <c r="B6" s="63"/>
-      <c r="C6" s="63"/>
+      <c r="A6" s="73" t="s">
+        <v>41</v>
+      </c>
+      <c r="B6" s="73"/>
+      <c r="C6" s="73"/>
       <c r="D6" s="4" t="str">
         <f>DATI_INPUT!C6</f>
         <v>IRS</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="63" t="s">
-        <v>43</v>
-      </c>
-      <c r="B7" s="63"/>
-      <c r="C7" s="63"/>
+      <c r="A7" s="73" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7" s="73"/>
+      <c r="C7" s="73"/>
       <c r="D7" s="2">
         <v>0.15</v>
       </c>
-      <c r="E7" s="58" t="s">
-        <v>44</v>
-      </c>
-      <c r="F7" s="58"/>
-      <c r="G7" s="58"/>
-      <c r="H7" s="58"/>
+      <c r="E7" s="68" t="s">
+        <v>43</v>
+      </c>
+      <c r="F7" s="68"/>
+      <c r="G7" s="68"/>
+      <c r="H7" s="68"/>
     </row>
     <row r="9" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="C9" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>26</v>
-      </c>
       <c r="D9" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E9" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="F9" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="G9" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="H9" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9474,13 +10498,13 @@
         <f>IFERROR(IF(DATI_INPUT!I20="Sì",getpl_fromnspt(DATI_INPUT!D20,DATI_INPUT!H20),IF(DATI_INPUT!F20="",0,DATI_INPUT!F20)),IF(DATI_INPUT!F20="",0,DATI_INPUT!F20))</f>
         <v>3</v>
       </c>
-      <c r="G17" s="18">
-        <f>IFERROR(IF(OR(C17="",F17=0),"",getqs(DATI_INPUT!D20,DATI_INPUT!C6,F17)),"")</f>
-        <v>0.41883573812024932</v>
+      <c r="G17" s="18" t="str">
+        <f ca="1">IFERROR(IF(OR(C17="",F17=0),"",getqs(DATI_INPUT!D20,DATI_INPUT!C6,F17)),"")</f>
+        <v/>
       </c>
       <c r="H17" s="19">
-        <f t="shared" si="0"/>
-        <v>592.11507507274507</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9550,69 +10574,69 @@
       </c>
     </row>
     <row r="20" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="64" t="s">
-        <v>50</v>
-      </c>
-      <c r="B20" s="64"/>
-      <c r="C20" s="64"/>
-      <c r="D20" s="64"/>
-      <c r="E20" s="64"/>
-      <c r="F20" s="64"/>
-      <c r="G20" s="64"/>
+      <c r="A20" s="74" t="s">
+        <v>49</v>
+      </c>
+      <c r="B20" s="74"/>
+      <c r="C20" s="74"/>
+      <c r="D20" s="74"/>
+      <c r="E20" s="74"/>
+      <c r="F20" s="74"/>
+      <c r="G20" s="74"/>
       <c r="H20" s="16">
         <f ca="1">SUM(H10:H19)</f>
-        <v>592.11507507274507</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="65" t="s">
-        <v>51</v>
-      </c>
-      <c r="B21" s="65"/>
-      <c r="C21" s="65"/>
-      <c r="D21" s="65"/>
-      <c r="E21" s="65"/>
-      <c r="F21" s="65"/>
-      <c r="G21" s="65"/>
+      <c r="A21" s="75" t="s">
+        <v>50</v>
+      </c>
+      <c r="B21" s="75"/>
+      <c r="C21" s="75"/>
+      <c r="D21" s="75"/>
+      <c r="E21" s="75"/>
+      <c r="F21" s="75"/>
+      <c r="G21" s="75"/>
       <c r="H21" s="19">
         <f ca="1">D7*H20</f>
-        <v>88.817261260911764</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="66" t="s">
-        <v>52</v>
-      </c>
-      <c r="B22" s="66"/>
-      <c r="C22" s="66"/>
-      <c r="D22" s="66"/>
-      <c r="E22" s="66"/>
-      <c r="F22" s="66"/>
-      <c r="G22" s="66"/>
+      <c r="A22" s="76" t="s">
+        <v>51</v>
+      </c>
+      <c r="B22" s="76"/>
+      <c r="C22" s="76"/>
+      <c r="D22" s="76"/>
+      <c r="E22" s="76"/>
+      <c r="F22" s="76"/>
+      <c r="G22" s="76"/>
       <c r="H22" s="16">
         <f ca="1">H20+H21</f>
-        <v>680.93233633365685</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A6:C6"/>
     <mergeCell ref="A7:C7"/>
     <mergeCell ref="E7:H7"/>
     <mergeCell ref="A20:G20"/>
     <mergeCell ref="A21:G21"/>
     <mergeCell ref="A22:G22"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A6:C6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="95" fitToHeight="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Foglio5">
     <pageSetUpPr fitToPage="1"/>
@@ -9630,56 +10654,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="67" t="s">
+      <c r="A1" s="83" t="s">
+        <v>53</v>
+      </c>
+      <c r="B1" s="83"/>
+      <c r="C1" s="83"/>
+      <c r="D1" s="83"/>
+      <c r="E1" s="83"/>
+      <c r="F1" s="83"/>
+      <c r="G1" s="83"/>
+    </row>
+    <row r="2" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="84" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="67"/>
-      <c r="C1" s="67"/>
-      <c r="D1" s="67"/>
-      <c r="E1" s="67"/>
-      <c r="F1" s="67"/>
-      <c r="G1" s="67"/>
-    </row>
-    <row r="2" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="68" t="s">
+      <c r="B2" s="84"/>
+      <c r="C2" s="84"/>
+      <c r="D2" s="84"/>
+      <c r="E2" s="84"/>
+      <c r="F2" s="84"/>
+      <c r="G2" s="84"/>
+    </row>
+    <row r="4" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="82" t="s">
         <v>55</v>
       </c>
-      <c r="B2" s="68"/>
-      <c r="C2" s="68"/>
-      <c r="D2" s="68"/>
-      <c r="E2" s="68"/>
-      <c r="F2" s="68"/>
-      <c r="G2" s="68"/>
-    </row>
-    <row r="4" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="69" t="s">
-        <v>56</v>
-      </c>
-      <c r="B4" s="69"/>
-      <c r="C4" s="69"/>
-      <c r="D4" s="69"/>
-      <c r="E4" s="69"/>
-      <c r="F4" s="69"/>
-      <c r="G4" s="69"/>
+      <c r="B4" s="82"/>
+      <c r="C4" s="82"/>
+      <c r="D4" s="82"/>
+      <c r="E4" s="82"/>
+      <c r="F4" s="82"/>
+      <c r="G4" s="82"/>
     </row>
     <row r="5" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="B5" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="B5" s="20" t="s">
+      <c r="C5" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="C5" s="20" t="s">
+      <c r="D5" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="D5" s="20" t="s">
+      <c r="E5" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="E5" s="20" t="s">
-        <v>61</v>
-      </c>
       <c r="F5" s="20" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9699,7 +10723,7 @@
         <v>1.4</v>
       </c>
       <c r="F6" s="21" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9791,188 +10815,198 @@
         <v>1</v>
       </c>
       <c r="F11" s="4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="82" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="69" t="s">
-        <v>64</v>
-      </c>
-      <c r="B13" s="69"/>
-      <c r="C13" s="69"/>
-      <c r="D13" s="69"/>
-      <c r="E13" s="69"/>
-      <c r="F13" s="69"/>
-      <c r="G13" s="69"/>
+      <c r="B13" s="82"/>
+      <c r="C13" s="82"/>
+      <c r="D13" s="82"/>
+      <c r="E13" s="82"/>
+      <c r="F13" s="82"/>
+      <c r="G13" s="82"/>
     </row>
     <row r="14" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="B14" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="B14" s="20" t="s">
-        <v>66</v>
-      </c>
-      <c r="C14" s="70" t="s">
-        <v>36</v>
-      </c>
-      <c r="D14" s="70"/>
-      <c r="E14" s="70"/>
-      <c r="F14" s="70"/>
-      <c r="G14" s="70"/>
+      <c r="C14" s="85" t="s">
+        <v>35</v>
+      </c>
+      <c r="D14" s="85"/>
+      <c r="E14" s="85"/>
+      <c r="F14" s="85"/>
+      <c r="G14" s="85"/>
     </row>
     <row r="15" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="22" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B15" s="23">
         <v>1.1499999999999999</v>
       </c>
-      <c r="C15" s="71" t="s">
-        <v>68</v>
-      </c>
-      <c r="D15" s="71"/>
-      <c r="E15" s="71"/>
-      <c r="F15" s="71"/>
-      <c r="G15" s="71"/>
+      <c r="C15" s="80" t="s">
+        <v>67</v>
+      </c>
+      <c r="D15" s="80"/>
+      <c r="E15" s="80"/>
+      <c r="F15" s="80"/>
+      <c r="G15" s="80"/>
     </row>
     <row r="16" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="24" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B16" s="25">
         <v>1.25</v>
       </c>
-      <c r="C16" s="72"/>
-      <c r="D16" s="72"/>
-      <c r="E16" s="72"/>
-      <c r="F16" s="72"/>
-      <c r="G16" s="72"/>
+      <c r="C16" s="81"/>
+      <c r="D16" s="81"/>
+      <c r="E16" s="81"/>
+      <c r="F16" s="81"/>
+      <c r="G16" s="81"/>
     </row>
     <row r="17" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="22" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B17" s="23">
         <v>1.1499999999999999</v>
       </c>
-      <c r="C17" s="71"/>
-      <c r="D17" s="71"/>
-      <c r="E17" s="71"/>
-      <c r="F17" s="71"/>
-      <c r="G17" s="71"/>
+      <c r="C17" s="80"/>
+      <c r="D17" s="80"/>
+      <c r="E17" s="80"/>
+      <c r="F17" s="80"/>
+      <c r="G17" s="80"/>
     </row>
     <row r="19" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="69" t="s">
+      <c r="A19" s="82" t="s">
+        <v>70</v>
+      </c>
+      <c r="B19" s="82"/>
+      <c r="C19" s="82"/>
+      <c r="D19" s="82"/>
+      <c r="E19" s="82"/>
+      <c r="F19" s="82"/>
+      <c r="G19" s="82"/>
+    </row>
+    <row r="20" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="78" t="s">
         <v>71</v>
       </c>
-      <c r="B19" s="69"/>
-      <c r="C19" s="69"/>
-      <c r="D19" s="69"/>
-      <c r="E19" s="69"/>
-      <c r="F19" s="69"/>
-      <c r="G19" s="69"/>
-    </row>
-    <row r="20" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="73" t="s">
-        <v>72</v>
-      </c>
-      <c r="B20" s="73"/>
+      <c r="B20" s="78"/>
       <c r="C20" s="36">
         <f>DATI_INPUT!C8</f>
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="74" t="s">
-        <v>73</v>
-      </c>
-      <c r="B21" s="74"/>
+      <c r="A21" s="79" t="s">
+        <v>72</v>
+      </c>
+      <c r="B21" s="79"/>
       <c r="C21" s="36">
         <f ca="1">'CALCOLO-Qmedio'!H20</f>
-        <v>683.1320351125114</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="73" t="s">
-        <v>74</v>
-      </c>
-      <c r="B22" s="73"/>
+      <c r="A22" s="78" t="s">
+        <v>73</v>
+      </c>
+      <c r="B22" s="78"/>
       <c r="C22" s="36">
         <f ca="1">'CALCOLO-Qminimo'!H20</f>
-        <v>592.11507507274507</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="74" t="s">
-        <v>75</v>
-      </c>
-      <c r="B23" s="74"/>
+      <c r="A23" s="79" t="s">
+        <v>74</v>
+      </c>
+      <c r="B23" s="79"/>
       <c r="C23" s="37">
         <f>INDEX(D6:D11,MATCH(C20,A6:A11,1))</f>
         <v>1.4</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="73" t="s">
-        <v>76</v>
-      </c>
-      <c r="B24" s="73"/>
+      <c r="A24" s="78" t="s">
+        <v>75</v>
+      </c>
+      <c r="B24" s="78"/>
       <c r="C24" s="37">
         <f>INDEX(E6:E11,MATCH(C20,A6:A11,1))</f>
         <v>1.4</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="74" t="s">
-        <v>77</v>
-      </c>
-      <c r="B25" s="74"/>
+      <c r="A25" s="79" t="s">
+        <v>76</v>
+      </c>
+      <c r="B25" s="79"/>
       <c r="C25" s="37">
         <f ca="1">IFERROR(C21/C23,"")</f>
-        <v>487.95145365179388</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="73" t="s">
-        <v>78</v>
-      </c>
-      <c r="B26" s="73"/>
+      <c r="A26" s="78" t="s">
+        <v>77</v>
+      </c>
+      <c r="B26" s="78"/>
       <c r="C26" s="37">
         <f ca="1">IFERROR(C22/C24,"")</f>
-        <v>422.93933933767505</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="74" t="s">
-        <v>79</v>
-      </c>
-      <c r="B27" s="74"/>
+      <c r="A27" s="79" t="s">
+        <v>78</v>
+      </c>
+      <c r="B27" s="79"/>
       <c r="C27" s="38">
         <f ca="1">IFERROR(MIN(C25,C26),"")</f>
-        <v>422.93933933767505</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="73" t="s">
-        <v>80</v>
-      </c>
-      <c r="B28" s="73"/>
+      <c r="A28" s="78" t="s">
+        <v>79</v>
+      </c>
+      <c r="B28" s="78"/>
       <c r="C28" s="39">
         <v>1.1499999999999999</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="74" t="s">
-        <v>81</v>
-      </c>
-      <c r="B29" s="74"/>
+      <c r="A29" s="79" t="s">
+        <v>80</v>
+      </c>
+      <c r="B29" s="79"/>
       <c r="C29" s="40">
         <f ca="1">IFERROR(C27/C28,"")</f>
-        <v>367.77333855450007</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="C14:G14"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="A19:G19"/>
+    <mergeCell ref="A20:B20"/>
     <mergeCell ref="A26:B26"/>
     <mergeCell ref="A27:B27"/>
     <mergeCell ref="A28:B28"/>
@@ -9982,23 +11016,13 @@
     <mergeCell ref="A23:B23"/>
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C15:G15"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="C17:G17"/>
-    <mergeCell ref="A19:G19"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="C14:G14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="83" fitToHeight="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr codeName="Foglio6"/>
   <dimension ref="A1:N59"/>
@@ -10011,100 +11035,100 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="56" t="s">
+        <v>81</v>
+      </c>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="56"/>
+      <c r="J1" s="56"/>
+      <c r="K1" s="56"/>
+      <c r="L1" s="56"/>
+      <c r="M1" s="56"/>
+      <c r="N1" s="56"/>
+    </row>
+    <row r="2" spans="1:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="53" t="s">
         <v>82</v>
       </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
-      <c r="F1" s="46"/>
-      <c r="G1" s="46"/>
-      <c r="H1" s="46"/>
-      <c r="I1" s="46"/>
-      <c r="J1" s="46"/>
-      <c r="K1" s="46"/>
-      <c r="L1" s="46"/>
-      <c r="M1" s="46"/>
-      <c r="N1" s="46"/>
-    </row>
-    <row r="2" spans="1:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="50" t="s">
-        <v>83</v>
-      </c>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="50"/>
-      <c r="H2" s="50"/>
-      <c r="I2" s="50"/>
-      <c r="J2" s="50"/>
-      <c r="K2" s="50"/>
-      <c r="L2" s="50"/>
-      <c r="M2" s="50"/>
-      <c r="N2" s="50"/>
+      <c r="B2" s="53"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="53"/>
+      <c r="L2" s="53"/>
+      <c r="M2" s="53"/>
+      <c r="N2" s="53"/>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="26" t="s">
+        <v>83</v>
+      </c>
+      <c r="C4" s="26" t="s">
         <v>84</v>
       </c>
-      <c r="C4" s="26" t="s">
+      <c r="E4" s="26" t="s">
         <v>85</v>
       </c>
-      <c r="E4" s="26" t="s">
+      <c r="G4" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="G4" s="26" t="s">
+      <c r="I4" s="27" t="s">
         <v>87</v>
-      </c>
-      <c r="I4" s="27" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="28" t="s">
+        <v>88</v>
+      </c>
+      <c r="B5" s="28" t="s">
         <v>89</v>
       </c>
-      <c r="B5" s="28" t="s">
+      <c r="C5" s="28" t="s">
+        <v>88</v>
+      </c>
+      <c r="D5" s="28" t="s">
+        <v>89</v>
+      </c>
+      <c r="E5" s="28" t="s">
+        <v>88</v>
+      </c>
+      <c r="F5" s="28" t="s">
+        <v>89</v>
+      </c>
+      <c r="G5" s="28" t="s">
+        <v>88</v>
+      </c>
+      <c r="H5" s="28" t="s">
+        <v>89</v>
+      </c>
+      <c r="I5" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="J5" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="K5" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="L5" s="29" t="s">
         <v>90</v>
       </c>
-      <c r="C5" s="28" t="s">
-        <v>89</v>
-      </c>
-      <c r="D5" s="28" t="s">
-        <v>90</v>
-      </c>
-      <c r="E5" s="28" t="s">
-        <v>89</v>
-      </c>
-      <c r="F5" s="28" t="s">
-        <v>90</v>
-      </c>
-      <c r="G5" s="28" t="s">
-        <v>89</v>
-      </c>
-      <c r="H5" s="28" t="s">
-        <v>90</v>
-      </c>
-      <c r="I5" s="29" t="s">
-        <v>24</v>
-      </c>
-      <c r="J5" s="29" t="s">
-        <v>25</v>
-      </c>
-      <c r="K5" s="29" t="s">
+      <c r="M5" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="L5" s="29" t="s">
+      <c r="N5" s="29" t="s">
         <v>91</v>
-      </c>
-      <c r="M5" s="29" t="s">
-        <v>29</v>
-      </c>
-      <c r="N5" s="29" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11071,7 +12095,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr codeName="Foglio7"/>
   <dimension ref="A1:N58"/>
@@ -11084,100 +12108,100 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="56" t="s">
+        <v>92</v>
+      </c>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="56"/>
+      <c r="J1" s="56"/>
+      <c r="K1" s="56"/>
+      <c r="L1" s="56"/>
+      <c r="M1" s="56"/>
+      <c r="N1" s="56"/>
+    </row>
+    <row r="2" spans="1:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="53" t="s">
         <v>93</v>
       </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
-      <c r="F1" s="46"/>
-      <c r="G1" s="46"/>
-      <c r="H1" s="46"/>
-      <c r="I1" s="46"/>
-      <c r="J1" s="46"/>
-      <c r="K1" s="46"/>
-      <c r="L1" s="46"/>
-      <c r="M1" s="46"/>
-      <c r="N1" s="46"/>
-    </row>
-    <row r="2" spans="1:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="50" t="s">
-        <v>94</v>
-      </c>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="50"/>
-      <c r="H2" s="50"/>
-      <c r="I2" s="50"/>
-      <c r="J2" s="50"/>
-      <c r="K2" s="50"/>
-      <c r="L2" s="50"/>
-      <c r="M2" s="50"/>
-      <c r="N2" s="50"/>
+      <c r="B2" s="53"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="53"/>
+      <c r="L2" s="53"/>
+      <c r="M2" s="53"/>
+      <c r="N2" s="53"/>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="26" t="s">
+        <v>94</v>
+      </c>
+      <c r="C4" s="26" t="s">
         <v>95</v>
       </c>
-      <c r="C4" s="26" t="s">
-        <v>96</v>
-      </c>
       <c r="E4" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="G4" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="G4" s="26" t="s">
+      <c r="I4" s="27" t="s">
         <v>87</v>
-      </c>
-      <c r="I4" s="27" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="28" t="s">
+        <v>88</v>
+      </c>
+      <c r="B5" s="28" t="s">
         <v>89</v>
       </c>
-      <c r="B5" s="28" t="s">
+      <c r="C5" s="28" t="s">
+        <v>88</v>
+      </c>
+      <c r="D5" s="28" t="s">
+        <v>89</v>
+      </c>
+      <c r="E5" s="28" t="s">
+        <v>88</v>
+      </c>
+      <c r="F5" s="28" t="s">
+        <v>89</v>
+      </c>
+      <c r="G5" s="28" t="s">
+        <v>88</v>
+      </c>
+      <c r="H5" s="28" t="s">
+        <v>89</v>
+      </c>
+      <c r="I5" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="J5" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="K5" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="L5" s="29" t="s">
         <v>90</v>
       </c>
-      <c r="C5" s="28" t="s">
-        <v>89</v>
-      </c>
-      <c r="D5" s="28" t="s">
-        <v>90</v>
-      </c>
-      <c r="E5" s="28" t="s">
-        <v>89</v>
-      </c>
-      <c r="F5" s="28" t="s">
-        <v>90</v>
-      </c>
-      <c r="G5" s="28" t="s">
-        <v>89</v>
-      </c>
-      <c r="H5" s="28" t="s">
-        <v>90</v>
-      </c>
-      <c r="I5" s="29" t="s">
-        <v>24</v>
-      </c>
-      <c r="J5" s="29" t="s">
-        <v>25</v>
-      </c>
-      <c r="K5" s="29" t="s">
+      <c r="M5" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="L5" s="29" t="s">
+      <c r="N5" s="29" t="s">
         <v>91</v>
-      </c>
-      <c r="M5" s="29" t="s">
-        <v>29</v>
-      </c>
-      <c r="N5" s="29" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12322,543 +13346,6 @@
       </c>
       <c r="F58">
         <v>0.26219999999999999</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:N1"/>
-    <mergeCell ref="A2:N2"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <sheetPr codeName="Foglio8"/>
-  <dimension ref="A1:N22"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="8" width="9" customWidth="1"/>
-    <col min="9" max="9" width="7" customWidth="1"/>
-    <col min="10" max="10" width="16" customWidth="1"/>
-    <col min="11" max="14" width="11" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="46" t="s">
-        <v>97</v>
-      </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
-      <c r="F1" s="46"/>
-      <c r="G1" s="46"/>
-      <c r="H1" s="46"/>
-      <c r="I1" s="46"/>
-      <c r="J1" s="46"/>
-      <c r="K1" s="46"/>
-      <c r="L1" s="46"/>
-      <c r="M1" s="46"/>
-      <c r="N1" s="46"/>
-    </row>
-    <row r="2" spans="1:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="50" t="s">
-        <v>98</v>
-      </c>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="50"/>
-      <c r="H2" s="50"/>
-      <c r="I2" s="50"/>
-      <c r="J2" s="50"/>
-      <c r="K2" s="50"/>
-      <c r="L2" s="50"/>
-      <c r="M2" s="50"/>
-      <c r="N2" s="50"/>
-    </row>
-    <row r="4" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="26" t="s">
-        <v>99</v>
-      </c>
-      <c r="C4" s="26" t="s">
-        <v>100</v>
-      </c>
-      <c r="E4" s="26" t="s">
-        <v>86</v>
-      </c>
-      <c r="G4" s="26" t="s">
-        <v>87</v>
-      </c>
-      <c r="I4" s="27" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="28" t="s">
-        <v>89</v>
-      </c>
-      <c r="B5" s="28" t="s">
-        <v>90</v>
-      </c>
-      <c r="C5" s="28" t="s">
-        <v>89</v>
-      </c>
-      <c r="D5" s="28" t="s">
-        <v>90</v>
-      </c>
-      <c r="E5" s="28" t="s">
-        <v>89</v>
-      </c>
-      <c r="F5" s="28" t="s">
-        <v>90</v>
-      </c>
-      <c r="G5" s="28" t="s">
-        <v>89</v>
-      </c>
-      <c r="H5" s="28" t="s">
-        <v>90</v>
-      </c>
-      <c r="I5" s="29" t="s">
-        <v>24</v>
-      </c>
-      <c r="J5" s="29" t="s">
-        <v>25</v>
-      </c>
-      <c r="K5" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="L5" s="29" t="s">
-        <v>91</v>
-      </c>
-      <c r="M5" s="29" t="s">
-        <v>29</v>
-      </c>
-      <c r="N5" s="29" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>1.0162</v>
-      </c>
-      <c r="B6">
-        <v>0.1928</v>
-      </c>
-      <c r="C6">
-        <v>1.0189999999999999</v>
-      </c>
-      <c r="D6">
-        <v>0.1484</v>
-      </c>
-      <c r="E6">
-        <v>1.204</v>
-      </c>
-      <c r="F6">
-        <v>0.2288</v>
-      </c>
-      <c r="G6">
-        <v>3.5346000000000002</v>
-      </c>
-      <c r="H6">
-        <v>0.44169999999999998</v>
-      </c>
-      <c r="I6" s="30" t="e">
-        <f>IF(DATI_INPUT!D13="MC",DATI_INPUT!A13,NA())</f>
-        <v>#N/A</v>
-      </c>
-      <c r="J6" s="31" t="e">
-        <f>IF(DATI_INPUT!D13="MC",DATI_INPUT!B13,NA())</f>
-        <v>#N/A</v>
-      </c>
-      <c r="K6" s="32" t="e">
-        <f>IF(DATI_INPUT!D13="MC",IFERROR('CALCOLO-Qmedio'!F10,NA()),NA())</f>
-        <v>#N/A</v>
-      </c>
-      <c r="L6" s="32" t="e">
-        <f>IF(DATI_INPUT!D13="MC",IFERROR('CALCOLO-Qmedio'!G10,NA()),NA())</f>
-        <v>#N/A</v>
-      </c>
-      <c r="M6" s="32" t="e">
-        <f>IF(DATI_INPUT!D13="MC",IFERROR('CALCOLO-Qminimo'!F10,NA()),NA())</f>
-        <v>#N/A</v>
-      </c>
-      <c r="N6" s="32" t="e">
-        <f>IF(DATI_INPUT!D13="MC",IFERROR('CALCOLO-Qminimo'!G10,NA()),NA())</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>7.9931999999999999</v>
-      </c>
-      <c r="B7">
-        <v>0.68769999999999998</v>
-      </c>
-      <c r="C7">
-        <v>7.9814999999999996</v>
-      </c>
-      <c r="D7">
-        <v>0.50060000000000004</v>
-      </c>
-      <c r="E7">
-        <v>1.5159</v>
-      </c>
-      <c r="F7">
-        <v>0.24399999999999999</v>
-      </c>
-      <c r="G7">
-        <v>5.4132999999999996</v>
-      </c>
-      <c r="H7">
-        <v>0.36430000000000001</v>
-      </c>
-      <c r="I7" s="33" t="e">
-        <f>IF(DATI_INPUT!D14="MC",DATI_INPUT!A14,NA())</f>
-        <v>#N/A</v>
-      </c>
-      <c r="J7" s="34" t="e">
-        <f>IF(DATI_INPUT!D14="MC",DATI_INPUT!B14,NA())</f>
-        <v>#N/A</v>
-      </c>
-      <c r="K7" s="35" t="e">
-        <f>IF(DATI_INPUT!D14="MC",IFERROR('CALCOLO-Qmedio'!F11,NA()),NA())</f>
-        <v>#N/A</v>
-      </c>
-      <c r="L7" s="35" t="e">
-        <f>IF(DATI_INPUT!D14="MC",IFERROR('CALCOLO-Qmedio'!G11,NA()),NA())</f>
-        <v>#N/A</v>
-      </c>
-      <c r="M7" s="35" t="e">
-        <f>IF(DATI_INPUT!D14="MC",IFERROR('CALCOLO-Qminimo'!F11,NA()),NA())</f>
-        <v>#N/A</v>
-      </c>
-      <c r="N7" s="35" t="e">
-        <f>IF(DATI_INPUT!D14="MC",IFERROR('CALCOLO-Qminimo'!G11,NA()),NA())</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E8">
-        <v>1.8716999999999999</v>
-      </c>
-      <c r="F8">
-        <v>0.29409999999999997</v>
-      </c>
-      <c r="G8">
-        <v>5.6273999999999997</v>
-      </c>
-      <c r="H8">
-        <v>0.3634</v>
-      </c>
-      <c r="I8" s="30" t="e">
-        <f>IF(DATI_INPUT!D15="MC",DATI_INPUT!A15,NA())</f>
-        <v>#N/A</v>
-      </c>
-      <c r="J8" s="31" t="e">
-        <f>IF(DATI_INPUT!D15="MC",DATI_INPUT!B15,NA())</f>
-        <v>#N/A</v>
-      </c>
-      <c r="K8" s="32" t="e">
-        <f>IF(DATI_INPUT!D15="MC",IFERROR('CALCOLO-Qmedio'!F12,NA()),NA())</f>
-        <v>#N/A</v>
-      </c>
-      <c r="L8" s="32" t="e">
-        <f>IF(DATI_INPUT!D15="MC",IFERROR('CALCOLO-Qmedio'!G12,NA()),NA())</f>
-        <v>#N/A</v>
-      </c>
-      <c r="M8" s="32" t="e">
-        <f>IF(DATI_INPUT!D15="MC",IFERROR('CALCOLO-Qminimo'!F12,NA()),NA())</f>
-        <v>#N/A</v>
-      </c>
-      <c r="N8" s="32" t="e">
-        <f>IF(DATI_INPUT!D15="MC",IFERROR('CALCOLO-Qminimo'!G12,NA()),NA())</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E9">
-        <v>1.8864000000000001</v>
-      </c>
-      <c r="F9">
-        <v>0.25209999999999999</v>
-      </c>
-      <c r="I9" s="33" t="e">
-        <f>IF(DATI_INPUT!D16="MC",DATI_INPUT!A16,NA())</f>
-        <v>#N/A</v>
-      </c>
-      <c r="J9" s="34" t="e">
-        <f>IF(DATI_INPUT!D16="MC",DATI_INPUT!B16,NA())</f>
-        <v>#N/A</v>
-      </c>
-      <c r="K9" s="35" t="e">
-        <f>IF(DATI_INPUT!D16="MC",IFERROR('CALCOLO-Qmedio'!F13,NA()),NA())</f>
-        <v>#N/A</v>
-      </c>
-      <c r="L9" s="35" t="e">
-        <f>IF(DATI_INPUT!D16="MC",IFERROR('CALCOLO-Qmedio'!G13,NA()),NA())</f>
-        <v>#N/A</v>
-      </c>
-      <c r="M9" s="35" t="e">
-        <f>IF(DATI_INPUT!D16="MC",IFERROR('CALCOLO-Qminimo'!F13,NA()),NA())</f>
-        <v>#N/A</v>
-      </c>
-      <c r="N9" s="35" t="e">
-        <f>IF(DATI_INPUT!D16="MC",IFERROR('CALCOLO-Qminimo'!G13,NA()),NA())</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E10">
-        <v>2.0074999999999998</v>
-      </c>
-      <c r="F10">
-        <v>0.25209999999999999</v>
-      </c>
-      <c r="I10" s="30">
-        <f>IF(DATI_INPUT!D17="MC",DATI_INPUT!A17,NA())</f>
-        <v>5</v>
-      </c>
-      <c r="J10" s="31">
-        <f>IF(DATI_INPUT!D17="MC",DATI_INPUT!B17,NA())</f>
-        <v>0</v>
-      </c>
-      <c r="K10" s="32">
-        <f>IF(DATI_INPUT!D17="MC",IFERROR('CALCOLO-Qmedio'!F14,NA()),NA())</f>
-        <v>5</v>
-      </c>
-      <c r="L10" s="32" t="str">
-        <f ca="1">IF(DATI_INPUT!D17="MC",IFERROR('CALCOLO-Qmedio'!G14,NA()),NA())</f>
-        <v/>
-      </c>
-      <c r="M10" s="32">
-        <f>IF(DATI_INPUT!D17="MC",IFERROR('CALCOLO-Qminimo'!F14,NA()),NA())</f>
-        <v>6</v>
-      </c>
-      <c r="N10" s="32" t="str">
-        <f ca="1">IF(DATI_INPUT!D17="MC",IFERROR('CALCOLO-Qminimo'!G14,NA()),NA())</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E11">
-        <v>1.9451000000000001</v>
-      </c>
-      <c r="F11">
-        <v>0.22339999999999999</v>
-      </c>
-      <c r="I11" s="33">
-        <f>IF(DATI_INPUT!D18="MC",DATI_INPUT!A18,NA())</f>
-        <v>6</v>
-      </c>
-      <c r="J11" s="34">
-        <f>IF(DATI_INPUT!D18="MC",DATI_INPUT!B18,NA())</f>
-        <v>0</v>
-      </c>
-      <c r="K11" s="35">
-        <f>IF(DATI_INPUT!D18="MC",IFERROR('CALCOLO-Qmedio'!F15,NA()),NA())</f>
-        <v>0</v>
-      </c>
-      <c r="L11" s="35" t="str">
-        <f>IF(DATI_INPUT!D18="MC",IFERROR('CALCOLO-Qmedio'!G15,NA()),NA())</f>
-        <v/>
-      </c>
-      <c r="M11" s="35">
-        <f>IF(DATI_INPUT!D18="MC",IFERROR('CALCOLO-Qminimo'!F15,NA()),NA())</f>
-        <v>0</v>
-      </c>
-      <c r="N11" s="35" t="str">
-        <f>IF(DATI_INPUT!D18="MC",IFERROR('CALCOLO-Qminimo'!G15,NA()),NA())</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E12">
-        <v>2.0882000000000001</v>
-      </c>
-      <c r="F12">
-        <v>0.22520000000000001</v>
-      </c>
-      <c r="I12" s="30" t="e">
-        <f>IF(DATI_INPUT!D19="MC",DATI_INPUT!A19,NA())</f>
-        <v>#N/A</v>
-      </c>
-      <c r="J12" s="31" t="e">
-        <f>IF(DATI_INPUT!D19="MC",DATI_INPUT!B19,NA())</f>
-        <v>#N/A</v>
-      </c>
-      <c r="K12" s="32" t="e">
-        <f>IF(DATI_INPUT!D19="MC",IFERROR('CALCOLO-Qmedio'!F16,NA()),NA())</f>
-        <v>#N/A</v>
-      </c>
-      <c r="L12" s="32" t="e">
-        <f>IF(DATI_INPUT!D19="MC",IFERROR('CALCOLO-Qmedio'!G16,NA()),NA())</f>
-        <v>#N/A</v>
-      </c>
-      <c r="M12" s="32" t="e">
-        <f>IF(DATI_INPUT!D19="MC",IFERROR('CALCOLO-Qminimo'!F16,NA()),NA())</f>
-        <v>#N/A</v>
-      </c>
-      <c r="N12" s="32" t="e">
-        <f>IF(DATI_INPUT!D19="MC",IFERROR('CALCOLO-Qminimo'!G16,NA()),NA())</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E13">
-        <v>2.0257999999999998</v>
-      </c>
-      <c r="F13">
-        <v>0.29680000000000001</v>
-      </c>
-      <c r="I13" s="33" t="e">
-        <f>IF(DATI_INPUT!D20="MC",DATI_INPUT!A20,NA())</f>
-        <v>#N/A</v>
-      </c>
-      <c r="J13" s="34" t="e">
-        <f>IF(DATI_INPUT!D20="MC",DATI_INPUT!B20,NA())</f>
-        <v>#N/A</v>
-      </c>
-      <c r="K13" s="35" t="e">
-        <f>IF(DATI_INPUT!D20="MC",IFERROR('CALCOLO-Qmedio'!F17,NA()),NA())</f>
-        <v>#N/A</v>
-      </c>
-      <c r="L13" s="35" t="e">
-        <f>IF(DATI_INPUT!D20="MC",IFERROR('CALCOLO-Qmedio'!G17,NA()),NA())</f>
-        <v>#N/A</v>
-      </c>
-      <c r="M13" s="35" t="e">
-        <f>IF(DATI_INPUT!D20="MC",IFERROR('CALCOLO-Qminimo'!F17,NA()),NA())</f>
-        <v>#N/A</v>
-      </c>
-      <c r="N13" s="35" t="e">
-        <f>IF(DATI_INPUT!D20="MC",IFERROR('CALCOLO-Qminimo'!G17,NA()),NA())</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E14">
-        <v>2.4916999999999998</v>
-      </c>
-      <c r="F14">
-        <v>0.24399999999999999</v>
-      </c>
-      <c r="I14" s="30" t="e">
-        <f>IF(DATI_INPUT!D21="MC",DATI_INPUT!A21,NA())</f>
-        <v>#N/A</v>
-      </c>
-      <c r="J14" s="31" t="e">
-        <f>IF(DATI_INPUT!D21="MC",DATI_INPUT!B21,NA())</f>
-        <v>#N/A</v>
-      </c>
-      <c r="K14" s="32" t="e">
-        <f>IF(DATI_INPUT!D21="MC",IFERROR('CALCOLO-Qmedio'!F18,NA()),NA())</f>
-        <v>#N/A</v>
-      </c>
-      <c r="L14" s="32" t="e">
-        <f>IF(DATI_INPUT!D21="MC",IFERROR('CALCOLO-Qmedio'!G18,NA()),NA())</f>
-        <v>#N/A</v>
-      </c>
-      <c r="M14" s="32" t="e">
-        <f>IF(DATI_INPUT!D21="MC",IFERROR('CALCOLO-Qminimo'!F18,NA()),NA())</f>
-        <v>#N/A</v>
-      </c>
-      <c r="N14" s="32" t="e">
-        <f>IF(DATI_INPUT!D21="MC",IFERROR('CALCOLO-Qminimo'!G18,NA()),NA())</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E15">
-        <v>2.4990000000000001</v>
-      </c>
-      <c r="F15">
-        <v>0.19570000000000001</v>
-      </c>
-      <c r="I15" s="33" t="e">
-        <f>IF(DATI_INPUT!D22="MC",DATI_INPUT!A22,NA())</f>
-        <v>#N/A</v>
-      </c>
-      <c r="J15" s="34" t="e">
-        <f>IF(DATI_INPUT!D22="MC",DATI_INPUT!B22,NA())</f>
-        <v>#N/A</v>
-      </c>
-      <c r="K15" s="35" t="e">
-        <f>IF(DATI_INPUT!D22="MC",IFERROR('CALCOLO-Qmedio'!F19,NA()),NA())</f>
-        <v>#N/A</v>
-      </c>
-      <c r="L15" s="35" t="e">
-        <f>IF(DATI_INPUT!D22="MC",IFERROR('CALCOLO-Qmedio'!G19,NA()),NA())</f>
-        <v>#N/A</v>
-      </c>
-      <c r="M15" s="35" t="e">
-        <f>IF(DATI_INPUT!D22="MC",IFERROR('CALCOLO-Qminimo'!F19,NA()),NA())</f>
-        <v>#N/A</v>
-      </c>
-      <c r="N15" s="35" t="e">
-        <f>IF(DATI_INPUT!D22="MC",IFERROR('CALCOLO-Qminimo'!G19,NA()),NA())</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E16">
-        <v>3.0125999999999999</v>
-      </c>
-      <c r="F16">
-        <v>0.29499999999999998</v>
-      </c>
-    </row>
-    <row r="17" spans="5:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E17">
-        <v>3.3134999999999999</v>
-      </c>
-      <c r="F17">
-        <v>0.29859999999999998</v>
-      </c>
-    </row>
-    <row r="18" spans="5:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E18">
-        <v>3.5886</v>
-      </c>
-      <c r="F18">
-        <v>0.30220000000000002</v>
-      </c>
-    </row>
-    <row r="19" spans="5:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E19">
-        <v>3.6802999999999999</v>
-      </c>
-      <c r="F19">
-        <v>0.3004</v>
-      </c>
-    </row>
-    <row r="20" spans="5:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E20">
-        <v>4.0178000000000003</v>
-      </c>
-      <c r="F20">
-        <v>0.43109999999999998</v>
-      </c>
-    </row>
-    <row r="21" spans="5:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E21">
-        <v>5.0193000000000003</v>
-      </c>
-      <c r="F21">
-        <v>0.432</v>
-      </c>
-    </row>
-    <row r="22" spans="5:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E22">
-        <v>6.0098000000000003</v>
-      </c>
-      <c r="F22">
-        <v>0.44450000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/articolo_04_micropali/Micropali_BustamanteDoix_v1.0.xlsx
+++ b/articolo_04_micropali/Micropali_BustamanteDoix_v1.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Documents\_Francisco\_GitHub\franciscojmendez_Risorse\articolo_04_micropali\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B92F618-7AC8-4E27-B1A9-C739878B7CB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1679323C-B837-4C41-8A69-13C05CF256C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7320" yWindow="0" windowWidth="21600" windowHeight="13785" tabRatio="710" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="710" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DB_Abachi" sheetId="1" state="hidden" r:id="rId1"/>
@@ -1125,11 +1125,11 @@
     <xf numFmtId="0" fontId="33" fillId="13" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1137,8 +1137,8 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1166,6 +1166,9 @@
     <xf numFmtId="0" fontId="30" fillId="18" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1179,8 +1182,8 @@
     <xf numFmtId="0" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1194,28 +1197,25 @@
     <xf numFmtId="0" fontId="14" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -6427,7 +6427,7 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:absoluteAnchor>
     <xdr:pos x="0" y="0"/>
-    <xdr:ext cx="8376508" cy="5469924"/>
+    <xdr:ext cx="9293311" cy="6066824"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Grafico 1">
@@ -6460,7 +6460,7 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:absoluteAnchor>
     <xdr:pos x="0" y="0"/>
-    <xdr:ext cx="8376508" cy="5469924"/>
+    <xdr:ext cx="9293311" cy="6066824"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Grafico 1">
@@ -6493,7 +6493,7 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:absoluteAnchor>
     <xdr:pos x="0" y="0"/>
-    <xdr:ext cx="8376508" cy="5469924"/>
+    <xdr:ext cx="9293311" cy="6066824"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Grafico 1">
@@ -7509,40 +7509,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="56" t="s">
+      <c r="A1" s="52" t="s">
         <v>96</v>
       </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
-      <c r="J1" s="56"/>
-      <c r="K1" s="56"/>
-      <c r="L1" s="56"/>
-      <c r="M1" s="56"/>
-      <c r="N1" s="56"/>
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="52"/>
+      <c r="G1" s="52"/>
+      <c r="H1" s="52"/>
+      <c r="I1" s="52"/>
+      <c r="J1" s="52"/>
+      <c r="K1" s="52"/>
+      <c r="L1" s="52"/>
+      <c r="M1" s="52"/>
+      <c r="N1" s="52"/>
     </row>
     <row r="2" spans="1:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="53" t="s">
+      <c r="A2" s="56" t="s">
         <v>97</v>
       </c>
-      <c r="B2" s="53"/>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="53"/>
-      <c r="K2" s="53"/>
-      <c r="L2" s="53"/>
-      <c r="M2" s="53"/>
-      <c r="N2" s="53"/>
+      <c r="B2" s="56"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
+      <c r="K2" s="56"/>
+      <c r="L2" s="56"/>
+      <c r="M2" s="56"/>
+      <c r="N2" s="56"/>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="26" t="s">
@@ -7823,19 +7823,19 @@
         <v>0</v>
       </c>
       <c r="K11" s="35">
-        <f>IF(DATI_INPUT!D18="MC",IFERROR('CALCOLO-Qmedio'!F15,NA()),NA())</f>
+        <f ca="1">IF(DATI_INPUT!D18="MC",IFERROR('CALCOLO-Qmedio'!F15,NA()),NA())</f>
         <v>0</v>
       </c>
       <c r="L11" s="35" t="str">
-        <f>IF(DATI_INPUT!D18="MC",IFERROR('CALCOLO-Qmedio'!G15,NA()),NA())</f>
+        <f ca="1">IF(DATI_INPUT!D18="MC",IFERROR('CALCOLO-Qmedio'!G15,NA()),NA())</f>
         <v/>
       </c>
       <c r="M11" s="35">
-        <f>IF(DATI_INPUT!D18="MC",IFERROR('CALCOLO-Qminimo'!F15,NA()),NA())</f>
+        <f ca="1">IF(DATI_INPUT!D18="MC",IFERROR('CALCOLO-Qminimo'!F15,NA()),NA())</f>
         <v>0</v>
       </c>
       <c r="N11" s="35" t="str">
-        <f>IF(DATI_INPUT!D18="MC",IFERROR('CALCOLO-Qminimo'!G15,NA()),NA())</f>
+        <f ca="1">IF(DATI_INPUT!D18="MC",IFERROR('CALCOLO-Qminimo'!G15,NA()),NA())</f>
         <v/>
       </c>
     </row>
@@ -8046,40 +8046,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="56" t="s">
+      <c r="A1" s="52" t="s">
         <v>100</v>
       </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
-      <c r="J1" s="56"/>
-      <c r="K1" s="56"/>
-      <c r="L1" s="56"/>
-      <c r="M1" s="56"/>
-      <c r="N1" s="56"/>
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="52"/>
+      <c r="G1" s="52"/>
+      <c r="H1" s="52"/>
+      <c r="I1" s="52"/>
+      <c r="J1" s="52"/>
+      <c r="K1" s="52"/>
+      <c r="L1" s="52"/>
+      <c r="M1" s="52"/>
+      <c r="N1" s="52"/>
     </row>
     <row r="2" spans="1:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="53" t="s">
+      <c r="A2" s="56" t="s">
         <v>101</v>
       </c>
-      <c r="B2" s="53"/>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="53"/>
-      <c r="K2" s="53"/>
-      <c r="L2" s="53"/>
-      <c r="M2" s="53"/>
-      <c r="N2" s="53"/>
+      <c r="B2" s="56"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
+      <c r="K2" s="56"/>
+      <c r="L2" s="56"/>
+      <c r="M2" s="56"/>
+      <c r="N2" s="56"/>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="26" t="s">
@@ -8795,38 +8795,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="56" t="s">
+      <c r="A1" s="52" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
-      <c r="J1" s="56"/>
-      <c r="K1" s="56"/>
-      <c r="L1" s="56"/>
-      <c r="M1" s="56"/>
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="52"/>
+      <c r="G1" s="52"/>
+      <c r="H1" s="52"/>
+      <c r="I1" s="52"/>
+      <c r="J1" s="52"/>
+      <c r="K1" s="52"/>
+      <c r="L1" s="52"/>
+      <c r="M1" s="52"/>
     </row>
     <row r="3" spans="1:13" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="52" t="s">
+      <c r="A3" s="53" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="52"/>
-      <c r="C3" s="52"/>
-      <c r="D3" s="52"/>
-      <c r="E3" s="52"/>
-      <c r="F3" s="52"/>
-      <c r="G3" s="52"/>
-      <c r="H3" s="52"/>
-      <c r="I3" s="52"/>
-      <c r="J3" s="52"/>
-      <c r="K3" s="52"/>
-      <c r="L3" s="52"/>
-      <c r="M3" s="52"/>
+      <c r="B3" s="53"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="53"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="53"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="53"/>
+      <c r="I3" s="53"/>
+      <c r="J3" s="53"/>
+      <c r="K3" s="53"/>
+      <c r="L3" s="53"/>
+      <c r="M3" s="53"/>
     </row>
     <row r="4" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="54" t="s">
@@ -8920,38 +8920,38 @@
       <c r="M8" s="55"/>
     </row>
     <row r="10" spans="1:13" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="52" t="s">
+      <c r="A10" s="53" t="s">
         <v>22</v>
       </c>
-      <c r="B10" s="52"/>
-      <c r="C10" s="52"/>
-      <c r="D10" s="52"/>
-      <c r="E10" s="52"/>
-      <c r="F10" s="52"/>
-      <c r="G10" s="52"/>
-      <c r="H10" s="52"/>
-      <c r="I10" s="52"/>
-      <c r="J10" s="52"/>
-      <c r="K10" s="52"/>
-      <c r="L10" s="52"/>
-      <c r="M10" s="52"/>
+      <c r="B10" s="53"/>
+      <c r="C10" s="53"/>
+      <c r="D10" s="53"/>
+      <c r="E10" s="53"/>
+      <c r="F10" s="53"/>
+      <c r="G10" s="53"/>
+      <c r="H10" s="53"/>
+      <c r="I10" s="53"/>
+      <c r="J10" s="53"/>
+      <c r="K10" s="53"/>
+      <c r="L10" s="53"/>
+      <c r="M10" s="53"/>
     </row>
     <row r="11" spans="1:13" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="53" t="s">
+      <c r="A11" s="56" t="s">
         <v>160</v>
       </c>
-      <c r="B11" s="53"/>
-      <c r="C11" s="53"/>
-      <c r="D11" s="53"/>
-      <c r="E11" s="53"/>
-      <c r="F11" s="53"/>
-      <c r="G11" s="53"/>
-      <c r="H11" s="53"/>
-      <c r="I11" s="53"/>
-      <c r="J11" s="53"/>
-      <c r="K11" s="53"/>
-      <c r="L11" s="53"/>
-      <c r="M11" s="53"/>
+      <c r="B11" s="56"/>
+      <c r="C11" s="56"/>
+      <c r="D11" s="56"/>
+      <c r="E11" s="56"/>
+      <c r="F11" s="56"/>
+      <c r="G11" s="56"/>
+      <c r="H11" s="56"/>
+      <c r="I11" s="56"/>
+      <c r="J11" s="56"/>
+      <c r="K11" s="56"/>
+      <c r="L11" s="56"/>
+      <c r="M11" s="56"/>
     </row>
     <row r="12" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
@@ -9014,7 +9014,7 @@
         <v>15</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>36</v>
+        <v>123</v>
       </c>
       <c r="J13" s="5" t="str">
         <f ca="1">IFERROR(getalpha(D13,DATI_INPUT!C6),"–")</f>
@@ -9189,7 +9189,7 @@
         <v>80</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>36</v>
+        <v>123</v>
       </c>
       <c r="J18" s="8" t="str">
         <f ca="1">IFERROR(getalpha(D18,DATI_INPUT!C6),"–")</f>
@@ -9330,11 +9330,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="A3:M3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="D5:M5"/>
     <mergeCell ref="A10:M10"/>
     <mergeCell ref="A11:M11"/>
     <mergeCell ref="A6:B6"/>
@@ -9343,6 +9338,11 @@
     <mergeCell ref="D7:M7"/>
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="D8:M8"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A3:M3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="D5:M5"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" sqref="C6" xr:uid="{00000000-0002-0000-0100-000000000000}">
@@ -9635,78 +9635,78 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="72" t="s">
+      <c r="A1" s="67" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="72"/>
-      <c r="D1" s="72"/>
-      <c r="E1" s="72"/>
-      <c r="F1" s="72"/>
-      <c r="G1" s="72"/>
-      <c r="H1" s="72"/>
+      <c r="B1" s="67"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="67"/>
+      <c r="E1" s="67"/>
+      <c r="F1" s="67"/>
+      <c r="G1" s="67"/>
+      <c r="H1" s="67"/>
     </row>
     <row r="2" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="53" t="s">
+      <c r="A2" s="56" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="53"/>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
+      <c r="B2" s="56"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
     </row>
     <row r="4" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="52" t="s">
+      <c r="A4" s="53" t="s">
         <v>39</v>
       </c>
-      <c r="B4" s="52"/>
-      <c r="C4" s="52"/>
-      <c r="D4" s="52"/>
-      <c r="E4" s="52"/>
-      <c r="F4" s="52"/>
-      <c r="G4" s="52"/>
-      <c r="H4" s="52"/>
+      <c r="B4" s="53"/>
+      <c r="C4" s="53"/>
+      <c r="D4" s="53"/>
+      <c r="E4" s="53"/>
+      <c r="F4" s="53"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="53"/>
     </row>
     <row r="5" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="67" t="s">
+      <c r="A5" s="68" t="s">
         <v>40</v>
       </c>
-      <c r="B5" s="67"/>
-      <c r="C5" s="67"/>
+      <c r="B5" s="68"/>
+      <c r="C5" s="68"/>
       <c r="D5" s="4">
         <f>DATI_INPUT!C5</f>
         <v>0.15</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="67" t="s">
+      <c r="A6" s="68" t="s">
         <v>41</v>
       </c>
-      <c r="B6" s="67"/>
-      <c r="C6" s="67"/>
+      <c r="B6" s="68"/>
+      <c r="C6" s="68"/>
       <c r="D6" s="4" t="str">
         <f>DATI_INPUT!C6</f>
         <v>IRS</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="67" t="s">
+      <c r="A7" s="68" t="s">
         <v>42</v>
       </c>
-      <c r="B7" s="67"/>
-      <c r="C7" s="67"/>
+      <c r="B7" s="68"/>
+      <c r="C7" s="68"/>
       <c r="D7" s="2">
         <v>0.15</v>
       </c>
-      <c r="E7" s="68" t="s">
+      <c r="E7" s="69" t="s">
         <v>43</v>
       </c>
-      <c r="F7" s="68"/>
-      <c r="G7" s="68"/>
-      <c r="H7" s="68"/>
+      <c r="F7" s="69"/>
+      <c r="G7" s="69"/>
+      <c r="H7" s="69"/>
     </row>
     <row r="9" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
@@ -9755,15 +9755,15 @@
         <v>0.22499999999999998</v>
       </c>
       <c r="F10" s="11">
-        <f>IFERROR(IF(DATI_INPUT!I13="Sì",getpl_fromnspt(DATI_INPUT!D13,DATI_INPUT!G13),IF(DATI_INPUT!E13="",0,DATI_INPUT!E13)),IF(DATI_INPUT!E13="",0,DATI_INPUT!E13))</f>
+        <f ca="1">IFERROR(IF(DATI_INPUT!I13="Sì",getpl_fromnspt(DATI_INPUT!D13,DATI_INPUT!G13),IF(DATI_INPUT!E13="",0,DATI_INPUT!E13)),IF(DATI_INPUT!E13="",0,DATI_INPUT!E13))</f>
         <v>0</v>
       </c>
       <c r="G10" s="11" t="str">
-        <f>IFERROR(IF(OR(C10="",F10=0),"",getqs(DATI_INPUT!D13,DATI_INPUT!C6,F10)),"")</f>
+        <f ca="1">IFERROR(IF(OR(C10="",F10=0),"",getqs(DATI_INPUT!D13,DATI_INPUT!C6,F10)),"")</f>
         <v/>
       </c>
       <c r="H10" s="12">
-        <f t="shared" ref="H10:H19" si="0">IFERROR(IF(OR(C10="",G10=""),0,PI()*E10*G10*1000*C10),0)</f>
+        <f t="shared" ref="H10:H19" ca="1" si="0">IFERROR(IF(OR(C10="",G10=""),0,PI()*E10*G10*1000*C10),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -9920,15 +9920,15 @@
         <v>0.22499999999999998</v>
       </c>
       <c r="F15" s="14">
-        <f>IFERROR(IF(DATI_INPUT!I18="Sì",getpl_fromnspt(DATI_INPUT!D18,DATI_INPUT!G18),IF(DATI_INPUT!E18="",0,DATI_INPUT!E18)),IF(DATI_INPUT!E18="",0,DATI_INPUT!E18))</f>
+        <f ca="1">IFERROR(IF(DATI_INPUT!I18="Sì",getpl_fromnspt(DATI_INPUT!D18,DATI_INPUT!G18),IF(DATI_INPUT!E18="",0,DATI_INPUT!E18)),IF(DATI_INPUT!E18="",0,DATI_INPUT!E18))</f>
         <v>0</v>
       </c>
       <c r="G15" s="14" t="str">
-        <f>IFERROR(IF(OR(C15="",F15=0),"",getqs(DATI_INPUT!D18,DATI_INPUT!C6,F15)),"")</f>
+        <f ca="1">IFERROR(IF(OR(C15="",F15=0),"",getqs(DATI_INPUT!D18,DATI_INPUT!C6,F15)),"")</f>
         <v/>
       </c>
       <c r="H15" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -10065,45 +10065,45 @@
       </c>
     </row>
     <row r="20" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="69" t="s">
+      <c r="A20" s="70" t="s">
         <v>49</v>
       </c>
-      <c r="B20" s="69"/>
-      <c r="C20" s="69"/>
-      <c r="D20" s="69"/>
-      <c r="E20" s="69"/>
-      <c r="F20" s="69"/>
-      <c r="G20" s="69"/>
+      <c r="B20" s="70"/>
+      <c r="C20" s="70"/>
+      <c r="D20" s="70"/>
+      <c r="E20" s="70"/>
+      <c r="F20" s="70"/>
+      <c r="G20" s="70"/>
       <c r="H20" s="16">
         <f ca="1">SUM(H10:H19)</f>
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="70" t="s">
+      <c r="A21" s="71" t="s">
         <v>50</v>
       </c>
-      <c r="B21" s="70"/>
-      <c r="C21" s="70"/>
-      <c r="D21" s="70"/>
-      <c r="E21" s="70"/>
-      <c r="F21" s="70"/>
-      <c r="G21" s="70"/>
+      <c r="B21" s="71"/>
+      <c r="C21" s="71"/>
+      <c r="D21" s="71"/>
+      <c r="E21" s="71"/>
+      <c r="F21" s="71"/>
+      <c r="G21" s="71"/>
       <c r="H21" s="15">
         <f ca="1">D7*H20</f>
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="71" t="s">
+      <c r="A22" s="72" t="s">
         <v>51</v>
       </c>
-      <c r="B22" s="71"/>
-      <c r="C22" s="71"/>
-      <c r="D22" s="71"/>
-      <c r="E22" s="71"/>
-      <c r="F22" s="71"/>
-      <c r="G22" s="71"/>
+      <c r="B22" s="72"/>
+      <c r="C22" s="72"/>
+      <c r="D22" s="72"/>
+      <c r="E22" s="72"/>
+      <c r="F22" s="72"/>
+      <c r="G22" s="72"/>
       <c r="H22" s="16">
         <f ca="1">H20+H21</f>
         <v>0</v>
@@ -10111,16 +10111,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="E7:H7"/>
+    <mergeCell ref="A20:G20"/>
+    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="A22:G22"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A4:H4"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="E7:H7"/>
-    <mergeCell ref="A20:G20"/>
-    <mergeCell ref="A21:G21"/>
-    <mergeCell ref="A22:G22"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="95" fitToHeight="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -10144,78 +10144,78 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="56" t="s">
+      <c r="A1" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="52"/>
+      <c r="G1" s="52"/>
+      <c r="H1" s="52"/>
     </row>
     <row r="2" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="53" t="s">
+      <c r="A2" s="56" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="53"/>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
+      <c r="B2" s="56"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
     </row>
     <row r="4" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="77" t="s">
+      <c r="A4" s="73" t="s">
         <v>39</v>
       </c>
-      <c r="B4" s="77"/>
-      <c r="C4" s="77"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="77"/>
+      <c r="B4" s="73"/>
+      <c r="C4" s="73"/>
+      <c r="D4" s="73"/>
+      <c r="E4" s="73"/>
+      <c r="F4" s="73"/>
+      <c r="G4" s="73"/>
+      <c r="H4" s="73"/>
     </row>
     <row r="5" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="73" t="s">
+      <c r="A5" s="74" t="s">
         <v>40</v>
       </c>
-      <c r="B5" s="73"/>
-      <c r="C5" s="73"/>
+      <c r="B5" s="74"/>
+      <c r="C5" s="74"/>
       <c r="D5" s="4">
         <f>DATI_INPUT!C5</f>
         <v>0.15</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="73" t="s">
+      <c r="A6" s="74" t="s">
         <v>41</v>
       </c>
-      <c r="B6" s="73"/>
-      <c r="C6" s="73"/>
+      <c r="B6" s="74"/>
+      <c r="C6" s="74"/>
       <c r="D6" s="4" t="str">
         <f>DATI_INPUT!C6</f>
         <v>IRS</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="73" t="s">
+      <c r="A7" s="74" t="s">
         <v>42</v>
       </c>
-      <c r="B7" s="73"/>
-      <c r="C7" s="73"/>
+      <c r="B7" s="74"/>
+      <c r="C7" s="74"/>
       <c r="D7" s="2">
         <v>0.15</v>
       </c>
-      <c r="E7" s="68" t="s">
+      <c r="E7" s="69" t="s">
         <v>43</v>
       </c>
-      <c r="F7" s="68"/>
-      <c r="G7" s="68"/>
-      <c r="H7" s="68"/>
+      <c r="F7" s="69"/>
+      <c r="G7" s="69"/>
+      <c r="H7" s="69"/>
     </row>
     <row r="9" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
@@ -10264,15 +10264,15 @@
         <v>0.22499999999999998</v>
       </c>
       <c r="F10" s="11">
-        <f>IFERROR(IF(DATI_INPUT!I13="Sì",getpl_fromnspt(DATI_INPUT!D13,DATI_INPUT!H13),IF(DATI_INPUT!F13="",0,DATI_INPUT!F13)),IF(DATI_INPUT!F13="",0,DATI_INPUT!F13))</f>
+        <f ca="1">IFERROR(IF(DATI_INPUT!I13="Sì",getpl_fromnspt(DATI_INPUT!D13,DATI_INPUT!H13),IF(DATI_INPUT!F13="",0,DATI_INPUT!F13)),IF(DATI_INPUT!F13="",0,DATI_INPUT!F13))</f>
         <v>0</v>
       </c>
       <c r="G10" s="11" t="str">
-        <f>IFERROR(IF(OR(C10="",F10=0),"",getqs(DATI_INPUT!D13,DATI_INPUT!C6,F10)),"")</f>
+        <f ca="1">IFERROR(IF(OR(C10="",F10=0),"",getqs(DATI_INPUT!D13,DATI_INPUT!C6,F10)),"")</f>
         <v/>
       </c>
       <c r="H10" s="12">
-        <f t="shared" ref="H10:H19" si="0">IFERROR(IF(OR(C10="",G10=""),0,PI()*E10*G10*1000*C10),0)</f>
+        <f t="shared" ref="H10:H19" ca="1" si="0">IFERROR(IF(OR(C10="",G10=""),0,PI()*E10*G10*1000*C10),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -10429,15 +10429,15 @@
         <v>0.22499999999999998</v>
       </c>
       <c r="F15" s="18">
-        <f>IFERROR(IF(DATI_INPUT!I18="Sì",getpl_fromnspt(DATI_INPUT!D18,DATI_INPUT!H18),IF(DATI_INPUT!F18="",0,DATI_INPUT!F18)),IF(DATI_INPUT!F18="",0,DATI_INPUT!F18))</f>
+        <f ca="1">IFERROR(IF(DATI_INPUT!I18="Sì",getpl_fromnspt(DATI_INPUT!D18,DATI_INPUT!H18),IF(DATI_INPUT!F18="",0,DATI_INPUT!F18)),IF(DATI_INPUT!F18="",0,DATI_INPUT!F18))</f>
         <v>0</v>
       </c>
       <c r="G15" s="18" t="str">
-        <f>IFERROR(IF(OR(C15="",F15=0),"",getqs(DATI_INPUT!D18,DATI_INPUT!C6,F15)),"")</f>
+        <f ca="1">IFERROR(IF(OR(C15="",F15=0),"",getqs(DATI_INPUT!D18,DATI_INPUT!C6,F15)),"")</f>
         <v/>
       </c>
       <c r="H15" s="19">
-        <f t="shared" si="0"/>
+        <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -10574,45 +10574,45 @@
       </c>
     </row>
     <row r="20" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="74" t="s">
+      <c r="A20" s="75" t="s">
         <v>49</v>
       </c>
-      <c r="B20" s="74"/>
-      <c r="C20" s="74"/>
-      <c r="D20" s="74"/>
-      <c r="E20" s="74"/>
-      <c r="F20" s="74"/>
-      <c r="G20" s="74"/>
+      <c r="B20" s="75"/>
+      <c r="C20" s="75"/>
+      <c r="D20" s="75"/>
+      <c r="E20" s="75"/>
+      <c r="F20" s="75"/>
+      <c r="G20" s="75"/>
       <c r="H20" s="16">
         <f ca="1">SUM(H10:H19)</f>
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="75" t="s">
+      <c r="A21" s="76" t="s">
         <v>50</v>
       </c>
-      <c r="B21" s="75"/>
-      <c r="C21" s="75"/>
-      <c r="D21" s="75"/>
-      <c r="E21" s="75"/>
-      <c r="F21" s="75"/>
-      <c r="G21" s="75"/>
+      <c r="B21" s="76"/>
+      <c r="C21" s="76"/>
+      <c r="D21" s="76"/>
+      <c r="E21" s="76"/>
+      <c r="F21" s="76"/>
+      <c r="G21" s="76"/>
       <c r="H21" s="19">
         <f ca="1">D7*H20</f>
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="76" t="s">
+      <c r="A22" s="77" t="s">
         <v>51</v>
       </c>
-      <c r="B22" s="76"/>
-      <c r="C22" s="76"/>
-      <c r="D22" s="76"/>
-      <c r="E22" s="76"/>
-      <c r="F22" s="76"/>
-      <c r="G22" s="76"/>
+      <c r="B22" s="77"/>
+      <c r="C22" s="77"/>
+      <c r="D22" s="77"/>
+      <c r="E22" s="77"/>
+      <c r="F22" s="77"/>
+      <c r="G22" s="77"/>
       <c r="H22" s="16">
         <f ca="1">H20+H21</f>
         <v>0</v>
@@ -10620,16 +10620,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="E7:H7"/>
+    <mergeCell ref="A20:G20"/>
+    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="A22:G22"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A4:H4"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="E7:H7"/>
-    <mergeCell ref="A20:G20"/>
-    <mergeCell ref="A21:G21"/>
-    <mergeCell ref="A22:G22"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="95" fitToHeight="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -10654,37 +10654,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="83" t="s">
+      <c r="A1" s="78" t="s">
         <v>53</v>
       </c>
-      <c r="B1" s="83"/>
-      <c r="C1" s="83"/>
-      <c r="D1" s="83"/>
-      <c r="E1" s="83"/>
-      <c r="F1" s="83"/>
-      <c r="G1" s="83"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
     </row>
     <row r="2" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="84" t="s">
+      <c r="A2" s="79" t="s">
         <v>54</v>
       </c>
-      <c r="B2" s="84"/>
-      <c r="C2" s="84"/>
-      <c r="D2" s="84"/>
-      <c r="E2" s="84"/>
-      <c r="F2" s="84"/>
-      <c r="G2" s="84"/>
+      <c r="B2" s="79"/>
+      <c r="C2" s="79"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="79"/>
+      <c r="F2" s="79"/>
+      <c r="G2" s="79"/>
     </row>
     <row r="4" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="82" t="s">
+      <c r="A4" s="80" t="s">
         <v>55</v>
       </c>
-      <c r="B4" s="82"/>
-      <c r="C4" s="82"/>
-      <c r="D4" s="82"/>
-      <c r="E4" s="82"/>
-      <c r="F4" s="82"/>
-      <c r="G4" s="82"/>
+      <c r="B4" s="80"/>
+      <c r="C4" s="80"/>
+      <c r="D4" s="80"/>
+      <c r="E4" s="80"/>
+      <c r="F4" s="80"/>
+      <c r="G4" s="80"/>
     </row>
     <row r="5" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="20" t="s">
@@ -10819,15 +10819,15 @@
       </c>
     </row>
     <row r="13" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="82" t="s">
+      <c r="A13" s="80" t="s">
         <v>63</v>
       </c>
-      <c r="B13" s="82"/>
-      <c r="C13" s="82"/>
-      <c r="D13" s="82"/>
-      <c r="E13" s="82"/>
-      <c r="F13" s="82"/>
-      <c r="G13" s="82"/>
+      <c r="B13" s="80"/>
+      <c r="C13" s="80"/>
+      <c r="D13" s="80"/>
+      <c r="E13" s="80"/>
+      <c r="F13" s="80"/>
+      <c r="G13" s="80"/>
     </row>
     <row r="14" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="20" t="s">
@@ -10836,13 +10836,13 @@
       <c r="B14" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="C14" s="85" t="s">
+      <c r="C14" s="81" t="s">
         <v>35</v>
       </c>
-      <c r="D14" s="85"/>
-      <c r="E14" s="85"/>
-      <c r="F14" s="85"/>
-      <c r="G14" s="85"/>
+      <c r="D14" s="81"/>
+      <c r="E14" s="81"/>
+      <c r="F14" s="81"/>
+      <c r="G14" s="81"/>
     </row>
     <row r="15" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="22" t="s">
@@ -10851,13 +10851,13 @@
       <c r="B15" s="23">
         <v>1.1499999999999999</v>
       </c>
-      <c r="C15" s="80" t="s">
+      <c r="C15" s="82" t="s">
         <v>67</v>
       </c>
-      <c r="D15" s="80"/>
-      <c r="E15" s="80"/>
-      <c r="F15" s="80"/>
-      <c r="G15" s="80"/>
+      <c r="D15" s="82"/>
+      <c r="E15" s="82"/>
+      <c r="F15" s="82"/>
+      <c r="G15" s="82"/>
     </row>
     <row r="16" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="24" t="s">
@@ -10866,11 +10866,11 @@
       <c r="B16" s="25">
         <v>1.25</v>
       </c>
-      <c r="C16" s="81"/>
-      <c r="D16" s="81"/>
-      <c r="E16" s="81"/>
-      <c r="F16" s="81"/>
-      <c r="G16" s="81"/>
+      <c r="C16" s="83"/>
+      <c r="D16" s="83"/>
+      <c r="E16" s="83"/>
+      <c r="F16" s="83"/>
+      <c r="G16" s="83"/>
     </row>
     <row r="17" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="22" t="s">
@@ -10879,117 +10879,117 @@
       <c r="B17" s="23">
         <v>1.1499999999999999</v>
       </c>
-      <c r="C17" s="80"/>
-      <c r="D17" s="80"/>
-      <c r="E17" s="80"/>
-      <c r="F17" s="80"/>
-      <c r="G17" s="80"/>
+      <c r="C17" s="82"/>
+      <c r="D17" s="82"/>
+      <c r="E17" s="82"/>
+      <c r="F17" s="82"/>
+      <c r="G17" s="82"/>
     </row>
     <row r="19" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="82" t="s">
+      <c r="A19" s="80" t="s">
         <v>70</v>
       </c>
-      <c r="B19" s="82"/>
-      <c r="C19" s="82"/>
-      <c r="D19" s="82"/>
-      <c r="E19" s="82"/>
-      <c r="F19" s="82"/>
-      <c r="G19" s="82"/>
+      <c r="B19" s="80"/>
+      <c r="C19" s="80"/>
+      <c r="D19" s="80"/>
+      <c r="E19" s="80"/>
+      <c r="F19" s="80"/>
+      <c r="G19" s="80"/>
     </row>
     <row r="20" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="78" t="s">
+      <c r="A20" s="84" t="s">
         <v>71</v>
       </c>
-      <c r="B20" s="78"/>
+      <c r="B20" s="84"/>
       <c r="C20" s="36">
         <f>DATI_INPUT!C8</f>
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="79" t="s">
+      <c r="A21" s="85" t="s">
         <v>72</v>
       </c>
-      <c r="B21" s="79"/>
+      <c r="B21" s="85"/>
       <c r="C21" s="36">
         <f ca="1">'CALCOLO-Qmedio'!H20</f>
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="78" t="s">
+      <c r="A22" s="84" t="s">
         <v>73</v>
       </c>
-      <c r="B22" s="78"/>
+      <c r="B22" s="84"/>
       <c r="C22" s="36">
         <f ca="1">'CALCOLO-Qminimo'!H20</f>
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="79" t="s">
+      <c r="A23" s="85" t="s">
         <v>74</v>
       </c>
-      <c r="B23" s="79"/>
+      <c r="B23" s="85"/>
       <c r="C23" s="37">
         <f>INDEX(D6:D11,MATCH(C20,A6:A11,1))</f>
         <v>1.4</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="78" t="s">
+      <c r="A24" s="84" t="s">
         <v>75</v>
       </c>
-      <c r="B24" s="78"/>
+      <c r="B24" s="84"/>
       <c r="C24" s="37">
         <f>INDEX(E6:E11,MATCH(C20,A6:A11,1))</f>
         <v>1.4</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="79" t="s">
+      <c r="A25" s="85" t="s">
         <v>76</v>
       </c>
-      <c r="B25" s="79"/>
+      <c r="B25" s="85"/>
       <c r="C25" s="37">
         <f ca="1">IFERROR(C21/C23,"")</f>
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="78" t="s">
+      <c r="A26" s="84" t="s">
         <v>77</v>
       </c>
-      <c r="B26" s="78"/>
+      <c r="B26" s="84"/>
       <c r="C26" s="37">
         <f ca="1">IFERROR(C22/C24,"")</f>
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="79" t="s">
+      <c r="A27" s="85" t="s">
         <v>78</v>
       </c>
-      <c r="B27" s="79"/>
+      <c r="B27" s="85"/>
       <c r="C27" s="38">
         <f ca="1">IFERROR(MIN(C25,C26),"")</f>
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="78" t="s">
+      <c r="A28" s="84" t="s">
         <v>79</v>
       </c>
-      <c r="B28" s="78"/>
+      <c r="B28" s="84"/>
       <c r="C28" s="39">
         <v>1.1499999999999999</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="79" t="s">
+      <c r="A29" s="85" t="s">
         <v>80</v>
       </c>
-      <c r="B29" s="79"/>
+      <c r="B29" s="85"/>
       <c r="C29" s="40">
         <f ca="1">IFERROR(C27/C28,"")</f>
         <v>0</v>
@@ -10997,16 +10997,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="C14:G14"/>
-    <mergeCell ref="C15:G15"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="C17:G17"/>
-    <mergeCell ref="A19:G19"/>
-    <mergeCell ref="A20:B20"/>
     <mergeCell ref="A26:B26"/>
     <mergeCell ref="A27:B27"/>
     <mergeCell ref="A28:B28"/>
@@ -11016,6 +11006,16 @@
     <mergeCell ref="A23:B23"/>
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="A19:G19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="C14:G14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="83" fitToHeight="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -11035,40 +11035,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="56" t="s">
+      <c r="A1" s="52" t="s">
         <v>81</v>
       </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
-      <c r="J1" s="56"/>
-      <c r="K1" s="56"/>
-      <c r="L1" s="56"/>
-      <c r="M1" s="56"/>
-      <c r="N1" s="56"/>
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="52"/>
+      <c r="G1" s="52"/>
+      <c r="H1" s="52"/>
+      <c r="I1" s="52"/>
+      <c r="J1" s="52"/>
+      <c r="K1" s="52"/>
+      <c r="L1" s="52"/>
+      <c r="M1" s="52"/>
+      <c r="N1" s="52"/>
     </row>
     <row r="2" spans="1:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="53" t="s">
+      <c r="A2" s="56" t="s">
         <v>82</v>
       </c>
-      <c r="B2" s="53"/>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="53"/>
-      <c r="K2" s="53"/>
-      <c r="L2" s="53"/>
-      <c r="M2" s="53"/>
-      <c r="N2" s="53"/>
+      <c r="B2" s="56"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
+      <c r="K2" s="56"/>
+      <c r="L2" s="56"/>
+      <c r="M2" s="56"/>
+      <c r="N2" s="56"/>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="26" t="s">
@@ -12108,40 +12108,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="56" t="s">
+      <c r="A1" s="52" t="s">
         <v>92</v>
       </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
-      <c r="J1" s="56"/>
-      <c r="K1" s="56"/>
-      <c r="L1" s="56"/>
-      <c r="M1" s="56"/>
-      <c r="N1" s="56"/>
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="52"/>
+      <c r="G1" s="52"/>
+      <c r="H1" s="52"/>
+      <c r="I1" s="52"/>
+      <c r="J1" s="52"/>
+      <c r="K1" s="52"/>
+      <c r="L1" s="52"/>
+      <c r="M1" s="52"/>
+      <c r="N1" s="52"/>
     </row>
     <row r="2" spans="1:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="53" t="s">
+      <c r="A2" s="56" t="s">
         <v>93</v>
       </c>
-      <c r="B2" s="53"/>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="53"/>
-      <c r="K2" s="53"/>
-      <c r="L2" s="53"/>
-      <c r="M2" s="53"/>
-      <c r="N2" s="53"/>
+      <c r="B2" s="56"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
+      <c r="K2" s="56"/>
+      <c r="L2" s="56"/>
+      <c r="M2" s="56"/>
+      <c r="N2" s="56"/>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="26" t="s">
@@ -12238,19 +12238,19 @@
         <v>0</v>
       </c>
       <c r="K6" s="32">
-        <f>IF(DATI_INPUT!D13="AL",IFERROR('CALCOLO-Qmedio'!F10,NA()),NA())</f>
+        <f ca="1">IF(DATI_INPUT!D13="AL",IFERROR('CALCOLO-Qmedio'!F10,NA()),NA())</f>
         <v>0</v>
       </c>
       <c r="L6" s="32" t="str">
-        <f>IF(DATI_INPUT!D13="AL",IFERROR('CALCOLO-Qmedio'!G10,NA()),NA())</f>
+        <f ca="1">IF(DATI_INPUT!D13="AL",IFERROR('CALCOLO-Qmedio'!G10,NA()),NA())</f>
         <v/>
       </c>
       <c r="M6" s="32">
-        <f>IF(DATI_INPUT!D13="AL",IFERROR('CALCOLO-Qminimo'!F10,NA()),NA())</f>
+        <f ca="1">IF(DATI_INPUT!D13="AL",IFERROR('CALCOLO-Qminimo'!F10,NA()),NA())</f>
         <v>0</v>
       </c>
       <c r="N6" s="32" t="str">
-        <f>IF(DATI_INPUT!D13="AL",IFERROR('CALCOLO-Qminimo'!G10,NA()),NA())</f>
+        <f ca="1">IF(DATI_INPUT!D13="AL",IFERROR('CALCOLO-Qminimo'!G10,NA()),NA())</f>
         <v/>
       </c>
     </row>
